--- a/Luban/Config/Datas/RoundData.xlsx
+++ b/Luban/Config/Datas/RoundData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1147,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="2"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="F5" s="0" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F6" s="0" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" customFormat="1" s="2">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="F12" s="0" t="n">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="L12" s="13" t="n"/>
       <c r="M12" s="13" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="F13" s="0" t="n">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="L13" s="13" t="n"/>
       <c r="M13" s="13" t="n"/>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="F14" s="0" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="F15" s="0" t="n">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="L15" s="13" t="n"/>
       <c r="M15" s="13" t="n"/>
@@ -1582,6 +1582,594 @@
     </row>
     <row r="22">
       <c r="D22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>第 13 回合</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>第 14 回合</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>第 15 回合</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>第 16 回合</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>第 17 回合</t>
+        </is>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>第 18 回合</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>第 19 回合</t>
+        </is>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>第 20 回合</t>
+        </is>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>第 21 回合</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>第 22 回合</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>第 23 回合</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>第 24 回合</t>
+        </is>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>第 25 回合</t>
+        </is>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>第 26 回合</t>
+        </is>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>第 27 回合</t>
+        </is>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>第 28 回合</t>
+        </is>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>第 29 回合</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>第 30 回合</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>第 31 回合</t>
+        </is>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>第 32 回合</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>第 33 回合</t>
+        </is>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>第 34 回合</t>
+        </is>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>第 35 回合</t>
+        </is>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>第 36 回合</t>
+        </is>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>第 37 回合</t>
+        </is>
+      </c>
+      <c r="F47" s="0" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>第 38 回合</t>
+        </is>
+      </c>
+      <c r="F48" s="0" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>第 39 回合</t>
+        </is>
+      </c>
+      <c r="F49" s="0" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>第 40 回合</t>
+        </is>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>186</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Config/Datas/RoundData.xlsx
+++ b/Luban/Config/Datas/RoundData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1147,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="2"/>
@@ -2169,6 +2169,741 @@
       </c>
       <c r="F50" s="0" t="n">
         <v>186</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>第 41 回合</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>第 42 回合</t>
+        </is>
+      </c>
+      <c r="F52" s="0" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>第 43 回合</t>
+        </is>
+      </c>
+      <c r="F53" s="0" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>第 44 回合</t>
+        </is>
+      </c>
+      <c r="F54" s="0" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>第 45 回合</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>第 46 回合</t>
+        </is>
+      </c>
+      <c r="F56" s="0" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>第 47 回合</t>
+        </is>
+      </c>
+      <c r="F57" s="0" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>第 48 回合</t>
+        </is>
+      </c>
+      <c r="F58" s="0" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>第 49 回合</t>
+        </is>
+      </c>
+      <c r="F59" s="0" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>第 50 回合</t>
+        </is>
+      </c>
+      <c r="F60" s="0" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>第 51 回合</t>
+        </is>
+      </c>
+      <c r="F61" s="0" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>第 52 回合</t>
+        </is>
+      </c>
+      <c r="F62" s="0" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>第 53 回合</t>
+        </is>
+      </c>
+      <c r="F63" s="0" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>第 54 回合</t>
+        </is>
+      </c>
+      <c r="F64" s="0" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D65" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t>第 55 回合</t>
+        </is>
+      </c>
+      <c r="F65" s="0" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D66" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t>第 56 回合</t>
+        </is>
+      </c>
+      <c r="F66" s="0" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>第 57 回合</t>
+        </is>
+      </c>
+      <c r="F67" s="0" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D68" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t>第 58 回合</t>
+        </is>
+      </c>
+      <c r="F68" s="0" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t>第 59 回合</t>
+        </is>
+      </c>
+      <c r="F69" s="0" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t>第 60 回合</t>
+        </is>
+      </c>
+      <c r="F70" s="0" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D71" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
+        <is>
+          <t>第 61 回合</t>
+        </is>
+      </c>
+      <c r="F71" s="0" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D72" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t>第 62 回合</t>
+        </is>
+      </c>
+      <c r="F72" s="0" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t>第 63 回合</t>
+        </is>
+      </c>
+      <c r="F73" s="0" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>第 64 回合</t>
+        </is>
+      </c>
+      <c r="F74" s="0" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D75" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t>第 65 回合</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D76" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t>第 66 回合</t>
+        </is>
+      </c>
+      <c r="F76" s="0" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>第 67 回合</t>
+        </is>
+      </c>
+      <c r="F77" s="0" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>第 68 回合</t>
+        </is>
+      </c>
+      <c r="F78" s="0" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>第 69 回合</t>
+        </is>
+      </c>
+      <c r="F79" s="0" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>第 70 回合</t>
+        </is>
+      </c>
+      <c r="F80" s="0" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D81" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>第 71 回合</t>
+        </is>
+      </c>
+      <c r="F81" s="0" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D82" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>第 72 回合</t>
+        </is>
+      </c>
+      <c r="F82" s="0" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>第 73 回合</t>
+        </is>
+      </c>
+      <c r="F83" s="0" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D84" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>第 74 回合</t>
+        </is>
+      </c>
+      <c r="F84" s="0" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D85" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E85" s="0" t="inlineStr">
+        <is>
+          <t>第 75 回合</t>
+        </is>
+      </c>
+      <c r="F85" s="0" t="n">
+        <v>326</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/RoundData.xlsx
+++ b/Luban/Config/Datas/RoundData.xlsx
@@ -1147,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="2"/>
@@ -2904,6 +2904,531 @@
       </c>
       <c r="F85" s="0" t="n">
         <v>326</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>76</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>第 76 回合</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>77</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>第 77 回合</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>78</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>第 78 回合</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>79</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>第 79 回合</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>80</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>第 80 回合</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>81</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>第 81 回合</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>82</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>第 82 回合</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>83</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>第 83 回合</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>84</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>第 84 回合</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>85</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>第 85 回合</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>86</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>第 86 回合</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>87</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>第 87 回合</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>88</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>第 88 回合</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>89</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>第 89 回合</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>90</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>第 90 回合</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>91</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>第 91 回合</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>92</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>第 92 回合</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>93</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>第 93 回合</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>94</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>第 94 回合</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>95</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>第 95 回合</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>96</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>第 96 回合</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>97</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>第 97 回合</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>98</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>第 98 回合</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>99</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>第 99 回合</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>100</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>第 100 回合</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>426</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/RoundData.xlsx
+++ b/Luban/Config/Datas/RoundData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1147,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M410"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="2"/>
@@ -1260,15 +1260,15 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>第 1 回合</t>
+          <t>第 1/20 波</t>
         </is>
       </c>
       <c r="F4" s="0" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -1281,15 +1281,15 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>第 2 回合</t>
+          <t>第 2/20 波</t>
         </is>
       </c>
       <c r="F5" s="0" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -1302,15 +1302,15 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>第 3 回合</t>
+          <t>第 3/20 波</t>
         </is>
       </c>
       <c r="F6" s="0" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="1" s="2">
@@ -1324,15 +1324,15 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>第 4 回合</t>
+          <t>第 4/20 波</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
@@ -1352,15 +1352,15 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>第 5 回合</t>
+          <t>第 5/20 波</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
@@ -1381,15 +1381,15 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>第 6 回合</t>
+          <t>第 6/20 波</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
@@ -1409,15 +1409,15 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>第 7 回合</t>
+          <t>第 7/20 波</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
@@ -1438,15 +1438,15 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>第 8 回合</t>
+          <t>第 8/20 波</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
@@ -1466,15 +1466,15 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>第 9 回合</t>
+          <t>第 9/20 波</t>
         </is>
       </c>
       <c r="F12" s="0" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="L12" s="13" t="n"/>
       <c r="M12" s="13" t="n"/>
@@ -1489,15 +1489,15 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>第 10 回合</t>
+          <t>第 10/20 波</t>
         </is>
       </c>
       <c r="F13" s="0" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="L13" s="13" t="n"/>
       <c r="M13" s="13" t="n"/>
@@ -1512,15 +1512,15 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>第 11 回合</t>
+          <t>第 11/20 波</t>
         </is>
       </c>
       <c r="F14" s="0" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
@@ -1535,15 +1535,15 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t>第 12 回合</t>
+          <t>第 12/20 波</t>
         </is>
       </c>
       <c r="F15" s="0" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="L15" s="13" t="n"/>
       <c r="M15" s="13" t="n"/>
@@ -1593,15 +1593,15 @@
         </is>
       </c>
       <c r="D23" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>第 13 回合</t>
+          <t>第 13/20 波</t>
         </is>
       </c>
       <c r="F23" s="0" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1614,15 +1614,15 @@
         </is>
       </c>
       <c r="D24" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>第 14 回合</t>
+          <t>第 14/20 波</t>
         </is>
       </c>
       <c r="F24" s="0" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -1635,15 +1635,15 @@
         </is>
       </c>
       <c r="D25" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>第 15 回合</t>
+          <t>第 15/20 波</t>
         </is>
       </c>
       <c r="F25" s="0" t="n">
-        <v>86</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -1656,15 +1656,15 @@
         </is>
       </c>
       <c r="D26" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>第 16 回合</t>
+          <t>第 16/20 波</t>
         </is>
       </c>
       <c r="F26" s="0" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -1677,15 +1677,15 @@
         </is>
       </c>
       <c r="D27" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>第 17 回合</t>
+          <t>第 17/20 波</t>
         </is>
       </c>
       <c r="F27" s="0" t="n">
-        <v>94</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -1698,15 +1698,15 @@
         </is>
       </c>
       <c r="D28" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>第 18 回合</t>
+          <t>第 18/20 波</t>
         </is>
       </c>
       <c r="F28" s="0" t="n">
-        <v>98</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -1719,15 +1719,15 @@
         </is>
       </c>
       <c r="D29" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>第 19 回合</t>
+          <t>第 19/20 波</t>
         </is>
       </c>
       <c r="F29" s="0" t="n">
-        <v>102</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1740,15 +1740,15 @@
         </is>
       </c>
       <c r="D30" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>第 20 回合</t>
+          <t>第 20/20 波</t>
         </is>
       </c>
       <c r="F30" s="0" t="n">
-        <v>106</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -1761,15 +1761,15 @@
         </is>
       </c>
       <c r="D31" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>第 21 回合</t>
+          <t>第 1/20 波</t>
         </is>
       </c>
       <c r="F31" s="0" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -1782,15 +1782,15 @@
         </is>
       </c>
       <c r="D32" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>第 22 回合</t>
+          <t>第 2/20 波</t>
         </is>
       </c>
       <c r="F32" s="0" t="n">
-        <v>114</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -1803,15 +1803,15 @@
         </is>
       </c>
       <c r="D33" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>第 23 回合</t>
+          <t>第 3/20 波</t>
         </is>
       </c>
       <c r="F33" s="0" t="n">
-        <v>118</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -1824,15 +1824,15 @@
         </is>
       </c>
       <c r="D34" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>第 24 回合</t>
+          <t>第 4/20 波</t>
         </is>
       </c>
       <c r="F34" s="0" t="n">
-        <v>122</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -1845,15 +1845,15 @@
         </is>
       </c>
       <c r="D35" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>第 25 回合</t>
+          <t>第 5/20 波</t>
         </is>
       </c>
       <c r="F35" s="0" t="n">
-        <v>126</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -1866,15 +1866,15 @@
         </is>
       </c>
       <c r="D36" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>第 26 回合</t>
+          <t>第 6/20 波</t>
         </is>
       </c>
       <c r="F36" s="0" t="n">
-        <v>130</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1887,15 +1887,15 @@
         </is>
       </c>
       <c r="D37" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>第 27 回合</t>
+          <t>第 7/20 波</t>
         </is>
       </c>
       <c r="F37" s="0" t="n">
-        <v>134</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -1908,15 +1908,15 @@
         </is>
       </c>
       <c r="D38" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>第 28 回合</t>
+          <t>第 8/20 波</t>
         </is>
       </c>
       <c r="F38" s="0" t="n">
-        <v>138</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -1929,15 +1929,15 @@
         </is>
       </c>
       <c r="D39" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>第 29 回合</t>
+          <t>第 9/20 波</t>
         </is>
       </c>
       <c r="F39" s="0" t="n">
-        <v>142</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -1950,15 +1950,15 @@
         </is>
       </c>
       <c r="D40" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>第 30 回合</t>
+          <t>第 10/20 波</t>
         </is>
       </c>
       <c r="F40" s="0" t="n">
-        <v>146</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -1971,15 +1971,15 @@
         </is>
       </c>
       <c r="D41" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t>第 31 回合</t>
+          <t>第 11/20 波</t>
         </is>
       </c>
       <c r="F41" s="0" t="n">
-        <v>150</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -1992,15 +1992,15 @@
         </is>
       </c>
       <c r="D42" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>第 32 回合</t>
+          <t>第 12/20 波</t>
         </is>
       </c>
       <c r="F42" s="0" t="n">
-        <v>154</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -2013,15 +2013,15 @@
         </is>
       </c>
       <c r="D43" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t>第 33 回合</t>
+          <t>第 13/20 波</t>
         </is>
       </c>
       <c r="F43" s="0" t="n">
-        <v>158</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -2034,15 +2034,15 @@
         </is>
       </c>
       <c r="D44" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>第 34 回合</t>
+          <t>第 14/20 波</t>
         </is>
       </c>
       <c r="F44" s="0" t="n">
-        <v>162</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -2055,15 +2055,15 @@
         </is>
       </c>
       <c r="D45" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t>第 35 回合</t>
+          <t>第 15/20 波</t>
         </is>
       </c>
       <c r="F45" s="0" t="n">
-        <v>166</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -2076,15 +2076,15 @@
         </is>
       </c>
       <c r="D46" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>第 36 回合</t>
+          <t>第 16/20 波</t>
         </is>
       </c>
       <c r="F46" s="0" t="n">
-        <v>170</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -2097,15 +2097,15 @@
         </is>
       </c>
       <c r="D47" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>第 37 回合</t>
+          <t>第 17/20 波</t>
         </is>
       </c>
       <c r="F47" s="0" t="n">
-        <v>174</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
@@ -2118,15 +2118,15 @@
         </is>
       </c>
       <c r="D48" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>第 38 回合</t>
+          <t>第 18/20 波</t>
         </is>
       </c>
       <c r="F48" s="0" t="n">
-        <v>178</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -2139,15 +2139,15 @@
         </is>
       </c>
       <c r="D49" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>第 39 回合</t>
+          <t>第 19/20 波</t>
         </is>
       </c>
       <c r="F49" s="0" t="n">
-        <v>182</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
@@ -2160,15 +2160,15 @@
         </is>
       </c>
       <c r="D50" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>第 40 回合</t>
+          <t>第 20/20 波</t>
         </is>
       </c>
       <c r="F50" s="0" t="n">
-        <v>186</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -2181,15 +2181,15 @@
         </is>
       </c>
       <c r="D51" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>第 41 回合</t>
+          <t>第 1/20 波</t>
         </is>
       </c>
       <c r="F51" s="0" t="n">
-        <v>190</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -2202,15 +2202,15 @@
         </is>
       </c>
       <c r="D52" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t>第 42 回合</t>
+          <t>第 2/20 波</t>
         </is>
       </c>
       <c r="F52" s="0" t="n">
-        <v>194</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -2223,15 +2223,15 @@
         </is>
       </c>
       <c r="D53" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>第 43 回合</t>
+          <t>第 3/20 波</t>
         </is>
       </c>
       <c r="F53" s="0" t="n">
-        <v>198</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -2244,15 +2244,15 @@
         </is>
       </c>
       <c r="D54" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>第 44 回合</t>
+          <t>第 4/20 波</t>
         </is>
       </c>
       <c r="F54" s="0" t="n">
-        <v>202</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -2265,15 +2265,15 @@
         </is>
       </c>
       <c r="D55" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
-          <t>第 45 回合</t>
+          <t>第 5/20 波</t>
         </is>
       </c>
       <c r="F55" s="0" t="n">
-        <v>206</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
@@ -2286,15 +2286,15 @@
         </is>
       </c>
       <c r="D56" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
-          <t>第 46 回合</t>
+          <t>第 6/20 波</t>
         </is>
       </c>
       <c r="F56" s="0" t="n">
-        <v>210</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -2307,15 +2307,15 @@
         </is>
       </c>
       <c r="D57" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
-          <t>第 47 回合</t>
+          <t>第 7/20 波</t>
         </is>
       </c>
       <c r="F57" s="0" t="n">
-        <v>214</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -2328,15 +2328,15 @@
         </is>
       </c>
       <c r="D58" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t>第 48 回合</t>
+          <t>第 8/20 波</t>
         </is>
       </c>
       <c r="F58" s="0" t="n">
-        <v>218</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -2349,15 +2349,15 @@
         </is>
       </c>
       <c r="D59" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
-          <t>第 49 回合</t>
+          <t>第 9/20 波</t>
         </is>
       </c>
       <c r="F59" s="0" t="n">
-        <v>222</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -2370,15 +2370,15 @@
         </is>
       </c>
       <c r="D60" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
-          <t>第 50 回合</t>
+          <t>第 10/20 波</t>
         </is>
       </c>
       <c r="F60" s="0" t="n">
-        <v>226</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -2391,15 +2391,15 @@
         </is>
       </c>
       <c r="D61" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
-          <t>第 51 回合</t>
+          <t>第 11/20 波</t>
         </is>
       </c>
       <c r="F61" s="0" t="n">
-        <v>230</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
@@ -2412,15 +2412,15 @@
         </is>
       </c>
       <c r="D62" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
-          <t>第 52 回合</t>
+          <t>第 12/20 波</t>
         </is>
       </c>
       <c r="F62" s="0" t="n">
-        <v>234</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -2433,15 +2433,15 @@
         </is>
       </c>
       <c r="D63" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
-          <t>第 53 回合</t>
+          <t>第 13/20 波</t>
         </is>
       </c>
       <c r="F63" s="0" t="n">
-        <v>238</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -2454,15 +2454,15 @@
         </is>
       </c>
       <c r="D64" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
-          <t>第 54 回合</t>
+          <t>第 14/20 波</t>
         </is>
       </c>
       <c r="F64" s="0" t="n">
-        <v>242</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -2475,15 +2475,15 @@
         </is>
       </c>
       <c r="D65" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
-          <t>第 55 回合</t>
+          <t>第 15/20 波</t>
         </is>
       </c>
       <c r="F65" s="0" t="n">
-        <v>246</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -2496,15 +2496,15 @@
         </is>
       </c>
       <c r="D66" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
-          <t>第 56 回合</t>
+          <t>第 16/20 波</t>
         </is>
       </c>
       <c r="F66" s="0" t="n">
-        <v>250</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -2517,15 +2517,15 @@
         </is>
       </c>
       <c r="D67" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
-          <t>第 57 回合</t>
+          <t>第 17/20 波</t>
         </is>
       </c>
       <c r="F67" s="0" t="n">
-        <v>254</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -2538,15 +2538,15 @@
         </is>
       </c>
       <c r="D68" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>第 58 回合</t>
+          <t>第 18/20 波</t>
         </is>
       </c>
       <c r="F68" s="0" t="n">
-        <v>258</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
@@ -2559,15 +2559,15 @@
         </is>
       </c>
       <c r="D69" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
-          <t>第 59 回合</t>
+          <t>第 19/20 波</t>
         </is>
       </c>
       <c r="F69" s="0" t="n">
-        <v>262</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
@@ -2580,15 +2580,15 @@
         </is>
       </c>
       <c r="D70" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
-          <t>第 60 回合</t>
+          <t>第 20/20 波</t>
         </is>
       </c>
       <c r="F70" s="0" t="n">
-        <v>266</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
@@ -2601,15 +2601,15 @@
         </is>
       </c>
       <c r="D71" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
-          <t>第 61 回合</t>
+          <t>第 1/20 波</t>
         </is>
       </c>
       <c r="F71" s="0" t="n">
-        <v>270</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
@@ -2622,15 +2622,15 @@
         </is>
       </c>
       <c r="D72" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
-          <t>第 62 回合</t>
+          <t>第 2/20 波</t>
         </is>
       </c>
       <c r="F72" s="0" t="n">
-        <v>274</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -2643,15 +2643,15 @@
         </is>
       </c>
       <c r="D73" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
-          <t>第 63 回合</t>
+          <t>第 3/20 波</t>
         </is>
       </c>
       <c r="F73" s="0" t="n">
-        <v>278</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -2664,15 +2664,15 @@
         </is>
       </c>
       <c r="D74" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
-          <t>第 64 回合</t>
+          <t>第 4/20 波</t>
         </is>
       </c>
       <c r="F74" s="0" t="n">
-        <v>282</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -2685,15 +2685,15 @@
         </is>
       </c>
       <c r="D75" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
-          <t>第 65 回合</t>
+          <t>第 5/20 波</t>
         </is>
       </c>
       <c r="F75" s="0" t="n">
-        <v>286</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -2706,15 +2706,15 @@
         </is>
       </c>
       <c r="D76" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
-          <t>第 66 回合</t>
+          <t>第 6/20 波</t>
         </is>
       </c>
       <c r="F76" s="0" t="n">
-        <v>290</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -2727,15 +2727,15 @@
         </is>
       </c>
       <c r="D77" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
-          <t>第 67 回合</t>
+          <t>第 7/20 波</t>
         </is>
       </c>
       <c r="F77" s="0" t="n">
-        <v>294</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -2748,15 +2748,15 @@
         </is>
       </c>
       <c r="D78" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
-          <t>第 68 回合</t>
+          <t>第 8/20 波</t>
         </is>
       </c>
       <c r="F78" s="0" t="n">
-        <v>298</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -2769,15 +2769,15 @@
         </is>
       </c>
       <c r="D79" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t>第 69 回合</t>
+          <t>第 9/20 波</t>
         </is>
       </c>
       <c r="F79" s="0" t="n">
-        <v>302</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -2790,15 +2790,15 @@
         </is>
       </c>
       <c r="D80" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
-          <t>第 70 回合</t>
+          <t>第 10/20 波</t>
         </is>
       </c>
       <c r="F80" s="0" t="n">
-        <v>306</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -2811,15 +2811,15 @@
         </is>
       </c>
       <c r="D81" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
-          <t>第 71 回合</t>
+          <t>第 11/20 波</t>
         </is>
       </c>
       <c r="F81" s="0" t="n">
-        <v>310</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -2832,15 +2832,15 @@
         </is>
       </c>
       <c r="D82" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
-          <t>第 72 回合</t>
+          <t>第 12/20 波</t>
         </is>
       </c>
       <c r="F82" s="0" t="n">
-        <v>314</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -2853,15 +2853,15 @@
         </is>
       </c>
       <c r="D83" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
-          <t>第 73 回合</t>
+          <t>第 13/20 波</t>
         </is>
       </c>
       <c r="F83" s="0" t="n">
-        <v>318</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84">
@@ -2874,15 +2874,15 @@
         </is>
       </c>
       <c r="D84" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
-          <t>第 74 回合</t>
+          <t>第 14/20 波</t>
         </is>
       </c>
       <c r="F84" s="0" t="n">
-        <v>322</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -2895,540 +2895,6840 @@
         </is>
       </c>
       <c r="D85" s="0" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
-          <t>第 75 回合</t>
+          <t>第 15/20 波</t>
         </is>
       </c>
       <c r="F85" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D86" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F86" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F87" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D88" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F88" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D89" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F89" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F90" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D91" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F91" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D92" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F92" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F93" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F94" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F95" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F96" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F97" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F98" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F99" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F100" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F101" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F102" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F103" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F104" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D105" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F105" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D106" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F106" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D107" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F107" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D108" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F108" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F109" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F110" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F111" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F112" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F113" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F114" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="0" t="n">
+        <v>105</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F115" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F116" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="0" t="n">
+        <v>107</v>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F117" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="0" t="n">
+        <v>108</v>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F118" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="0" t="n">
+        <v>109</v>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F119" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F120" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="0" t="n">
+        <v>111</v>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F121" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="0" t="n">
+        <v>112</v>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F122" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="0" t="n">
+        <v>113</v>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F123" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="0" t="n">
+        <v>114</v>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F124" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="0" t="n">
+        <v>115</v>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F125" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="0" t="n">
+        <v>116</v>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F126" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="0" t="n">
+        <v>117</v>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F127" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="0" t="n">
+        <v>118</v>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F128" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="0" t="n">
+        <v>119</v>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F129" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F130" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="C131" s="0" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F131" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="0" t="n">
+        <v>122</v>
+      </c>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F132" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="0" t="n">
+        <v>123</v>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F133" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="0" t="n">
+        <v>124</v>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F134" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F135" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="0" t="n">
+        <v>126</v>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F136" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="0" t="n">
+        <v>127</v>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F137" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="0" t="n">
+        <v>128</v>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F138" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="0" t="n">
+        <v>129</v>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F139" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F140" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="0" t="n">
+        <v>131</v>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F141" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="0" t="n">
+        <v>132</v>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F142" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="0" t="n">
+        <v>133</v>
+      </c>
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F143" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="0" t="n">
+        <v>134</v>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F144" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F145" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="0" t="n">
+        <v>136</v>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F146" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="0" t="n">
+        <v>137</v>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F147" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="0" t="n">
+        <v>138</v>
+      </c>
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F148" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="0" t="n">
+        <v>139</v>
+      </c>
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F149" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="C150" s="0" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F150" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="0" t="n">
+        <v>141</v>
+      </c>
+      <c r="C151" s="0" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F151" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="0" t="n">
+        <v>142</v>
+      </c>
+      <c r="C152" s="0" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F152" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="0" t="n">
+        <v>143</v>
+      </c>
+      <c r="C153" s="0" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F153" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="0" t="n">
+        <v>144</v>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F154" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="0" t="n">
+        <v>145</v>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F155" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="0" t="n">
+        <v>146</v>
+      </c>
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F156" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="0" t="n">
+        <v>147</v>
+      </c>
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F157" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="0" t="n">
+        <v>148</v>
+      </c>
+      <c r="C158" s="0" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F158" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="0" t="n">
+        <v>149</v>
+      </c>
+      <c r="C159" s="0" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F159" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F160" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="0" t="n">
+        <v>151</v>
+      </c>
+      <c r="C161" s="0" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F161" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="0" t="n">
+        <v>152</v>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F162" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="0" t="n">
+        <v>153</v>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F163" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="0" t="n">
+        <v>154</v>
+      </c>
+      <c r="C164" s="0" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F164" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="0" t="n">
+        <v>155</v>
+      </c>
+      <c r="C165" s="0" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F165" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="0" t="n">
+        <v>156</v>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F166" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="0" t="n">
+        <v>157</v>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F167" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="0" t="n">
+        <v>158</v>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F168" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="0" t="n">
+        <v>159</v>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F169" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F170" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="0" t="n">
+        <v>161</v>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F171" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="0" t="n">
+        <v>162</v>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F172" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="0" t="n">
+        <v>163</v>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F173" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="0" t="n">
+        <v>164</v>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F174" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" s="0" t="n">
+        <v>165</v>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F175" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="0" t="n">
+        <v>166</v>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F176" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="0" t="n">
+        <v>167</v>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F177" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="0" t="n">
+        <v>168</v>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F178" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="0" t="n">
+        <v>169</v>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F179" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F180" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="0" t="n">
+        <v>171</v>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F181" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="0" t="n">
+        <v>172</v>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F182" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="0" t="n">
+        <v>173</v>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F183" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="0" t="n">
+        <v>174</v>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F184" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F185" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="0" t="n">
+        <v>176</v>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F186" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="0" t="n">
+        <v>177</v>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F187" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="0" t="n">
+        <v>178</v>
+      </c>
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F188" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="0" t="n">
+        <v>179</v>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F189" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F190" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" s="0" t="n">
+        <v>181</v>
+      </c>
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F191" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" s="0" t="n">
+        <v>182</v>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F192" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" s="0" t="n">
+        <v>183</v>
+      </c>
+      <c r="C193" s="0" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F193" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" s="0" t="n">
+        <v>184</v>
+      </c>
+      <c r="C194" s="0" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F194" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="C195" s="0" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F195" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" s="0" t="n">
+        <v>186</v>
+      </c>
+      <c r="C196" s="0" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F196" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" s="0" t="n">
+        <v>187</v>
+      </c>
+      <c r="C197" s="0" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F197" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" s="0" t="n">
+        <v>188</v>
+      </c>
+      <c r="C198" s="0" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F198" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" s="0" t="n">
+        <v>189</v>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F199" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" s="0" t="n">
+        <v>190</v>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F200" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" s="0" t="n">
+        <v>191</v>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F201" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" s="0" t="n">
+        <v>192</v>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F202" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" s="0" t="n">
+        <v>193</v>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F203" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" s="0" t="n">
+        <v>194</v>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F204" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" s="0" t="n">
+        <v>195</v>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F205" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" s="0" t="n">
+        <v>196</v>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F206" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" s="0" t="n">
+        <v>197</v>
+      </c>
+      <c r="C207" s="0" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F207" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" s="0" t="n">
+        <v>198</v>
+      </c>
+      <c r="C208" s="0" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F208" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" s="0" t="n">
+        <v>199</v>
+      </c>
+      <c r="C209" s="0" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F209" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="C210" s="0" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F210" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" s="0" t="n">
+        <v>201</v>
+      </c>
+      <c r="C211" s="0" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F211" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" s="0" t="n">
+        <v>202</v>
+      </c>
+      <c r="C212" s="0" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F212" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" s="0" t="n">
+        <v>203</v>
+      </c>
+      <c r="C213" s="0" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F213" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" s="0" t="n">
+        <v>204</v>
+      </c>
+      <c r="C214" s="0" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F214" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" s="0" t="n">
+        <v>205</v>
+      </c>
+      <c r="C215" s="0" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F215" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" s="0" t="n">
+        <v>206</v>
+      </c>
+      <c r="C216" s="0" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F216" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" s="0" t="n">
+        <v>207</v>
+      </c>
+      <c r="C217" s="0" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F217" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" s="0" t="n">
+        <v>208</v>
+      </c>
+      <c r="C218" s="0" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F218" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" s="0" t="n">
+        <v>209</v>
+      </c>
+      <c r="C219" s="0" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F219" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" s="0" t="n">
+        <v>210</v>
+      </c>
+      <c r="C220" s="0" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F220" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" s="0" t="n">
+        <v>211</v>
+      </c>
+      <c r="C221" s="0" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F221" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" s="0" t="n">
+        <v>212</v>
+      </c>
+      <c r="C222" s="0" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F222" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" s="0" t="n">
+        <v>213</v>
+      </c>
+      <c r="C223" s="0" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F223" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" s="0" t="n">
+        <v>214</v>
+      </c>
+      <c r="C224" s="0" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F224" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" s="0" t="n">
+        <v>215</v>
+      </c>
+      <c r="C225" s="0" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F225" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" s="0" t="n">
+        <v>216</v>
+      </c>
+      <c r="C226" s="0" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F226" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" s="0" t="n">
+        <v>217</v>
+      </c>
+      <c r="C227" s="0" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F227" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" s="0" t="n">
+        <v>218</v>
+      </c>
+      <c r="C228" s="0" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F228" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" s="0" t="n">
+        <v>219</v>
+      </c>
+      <c r="C229" s="0" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F229" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" s="0" t="n">
+        <v>220</v>
+      </c>
+      <c r="C230" s="0" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F230" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" s="0" t="n">
+        <v>221</v>
+      </c>
+      <c r="C231" s="0" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F231" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" s="0" t="n">
+        <v>222</v>
+      </c>
+      <c r="C232" s="0" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F232" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" s="0" t="n">
+        <v>223</v>
+      </c>
+      <c r="C233" s="0" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F233" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" s="0" t="n">
+        <v>224</v>
+      </c>
+      <c r="C234" s="0" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F234" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" s="0" t="n">
+        <v>225</v>
+      </c>
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F235" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" s="0" t="n">
+        <v>226</v>
+      </c>
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F236" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" s="0" t="n">
+        <v>227</v>
+      </c>
+      <c r="C237" s="0" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F237" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" s="0" t="n">
+        <v>228</v>
+      </c>
+      <c r="C238" s="0" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F238" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" s="0" t="n">
+        <v>229</v>
+      </c>
+      <c r="C239" s="0" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F239" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" s="0" t="n">
+        <v>230</v>
+      </c>
+      <c r="C240" s="0" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F240" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" s="0" t="n">
+        <v>231</v>
+      </c>
+      <c r="C241" s="0" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F241" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" s="0" t="n">
+        <v>232</v>
+      </c>
+      <c r="C242" s="0" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F242" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" s="0" t="n">
+        <v>233</v>
+      </c>
+      <c r="C243" s="0" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F243" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" s="0" t="n">
+        <v>234</v>
+      </c>
+      <c r="C244" s="0" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F244" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" s="0" t="n">
+        <v>235</v>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F245" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" s="0" t="n">
+        <v>236</v>
+      </c>
+      <c r="C246" s="0" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F246" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" s="0" t="n">
+        <v>237</v>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F247" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" s="0" t="n">
+        <v>238</v>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F248" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" s="0" t="n">
+        <v>239</v>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F249" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" s="0" t="n">
+        <v>240</v>
+      </c>
+      <c r="C250" s="0" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F250" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" s="0" t="n">
+        <v>241</v>
+      </c>
+      <c r="C251" s="0" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F251" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" s="0" t="n">
+        <v>242</v>
+      </c>
+      <c r="C252" s="0" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F252" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" s="0" t="n">
+        <v>243</v>
+      </c>
+      <c r="C253" s="0" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F253" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" s="0" t="n">
+        <v>244</v>
+      </c>
+      <c r="C254" s="0" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F254" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" s="0" t="n">
+        <v>245</v>
+      </c>
+      <c r="C255" s="0" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F255" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" s="0" t="n">
+        <v>246</v>
+      </c>
+      <c r="C256" s="0" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F256" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" s="0" t="n">
+        <v>247</v>
+      </c>
+      <c r="C257" s="0" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F257" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" s="0" t="n">
+        <v>248</v>
+      </c>
+      <c r="C258" s="0" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F258" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" s="0" t="n">
+        <v>249</v>
+      </c>
+      <c r="C259" s="0" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F259" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="C260" s="0" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F260" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" s="0" t="n">
+        <v>251</v>
+      </c>
+      <c r="C261" s="0" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F261" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" s="0" t="n">
+        <v>252</v>
+      </c>
+      <c r="C262" s="0" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F262" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" s="0" t="n">
+        <v>253</v>
+      </c>
+      <c r="C263" s="0" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F263" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" s="0" t="n">
+        <v>254</v>
+      </c>
+      <c r="C264" s="0" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F264" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" s="0" t="n">
+        <v>255</v>
+      </c>
+      <c r="C265" s="0" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F265" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" s="0" t="n">
+        <v>256</v>
+      </c>
+      <c r="C266" s="0" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F266" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" s="0" t="n">
+        <v>257</v>
+      </c>
+      <c r="C267" s="0" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F267" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" s="0" t="n">
+        <v>258</v>
+      </c>
+      <c r="C268" s="0" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F268" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" s="0" t="n">
+        <v>259</v>
+      </c>
+      <c r="C269" s="0" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F269" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" s="0" t="n">
+        <v>260</v>
+      </c>
+      <c r="C270" s="0" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F270" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" s="0" t="n">
+        <v>261</v>
+      </c>
+      <c r="C271" s="0" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F271" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" s="0" t="n">
+        <v>262</v>
+      </c>
+      <c r="C272" s="0" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F272" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" s="0" t="n">
+        <v>263</v>
+      </c>
+      <c r="C273" s="0" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F273" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="C274" s="0" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F274" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" s="0" t="n">
+        <v>265</v>
+      </c>
+      <c r="C275" s="0" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F275" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" s="0" t="n">
+        <v>266</v>
+      </c>
+      <c r="C276" s="0" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F276" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" s="0" t="n">
+        <v>267</v>
+      </c>
+      <c r="C277" s="0" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F277" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" s="0" t="n">
+        <v>268</v>
+      </c>
+      <c r="C278" s="0" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F278" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" s="0" t="n">
+        <v>269</v>
+      </c>
+      <c r="C279" s="0" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F279" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="C280" s="0" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F280" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" s="0" t="n">
+        <v>271</v>
+      </c>
+      <c r="C281" s="0" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F281" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="C282" s="0" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F282" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" s="0" t="n">
+        <v>273</v>
+      </c>
+      <c r="C283" s="0" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E283" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F283" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" s="0" t="n">
+        <v>274</v>
+      </c>
+      <c r="C284" s="0" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F284" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" s="0" t="n">
+        <v>275</v>
+      </c>
+      <c r="C285" s="0" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F285" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" s="0" t="n">
+        <v>276</v>
+      </c>
+      <c r="C286" s="0" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F286" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" s="0" t="n">
+        <v>277</v>
+      </c>
+      <c r="C287" s="0" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F287" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" s="0" t="n">
+        <v>278</v>
+      </c>
+      <c r="C288" s="0" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F288" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" s="0" t="n">
+        <v>279</v>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F289" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" s="0" t="n">
+        <v>280</v>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F290" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" s="0" t="n">
+        <v>281</v>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F291" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" s="0" t="n">
+        <v>282</v>
+      </c>
+      <c r="C292" s="0" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F292" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" s="0" t="n">
+        <v>283</v>
+      </c>
+      <c r="C293" s="0" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F293" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" s="0" t="n">
+        <v>284</v>
+      </c>
+      <c r="C294" s="0" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F294" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" s="0" t="n">
+        <v>285</v>
+      </c>
+      <c r="C295" s="0" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F295" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" s="0" t="n">
+        <v>286</v>
+      </c>
+      <c r="C296" s="0" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F296" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" s="0" t="n">
+        <v>287</v>
+      </c>
+      <c r="C297" s="0" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F297" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" s="0" t="n">
+        <v>288</v>
+      </c>
+      <c r="C298" s="0" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F298" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" s="0" t="n">
+        <v>289</v>
+      </c>
+      <c r="C299" s="0" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F299" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" s="0" t="n">
+        <v>290</v>
+      </c>
+      <c r="C300" s="0" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F300" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" s="0" t="n">
+        <v>291</v>
+      </c>
+      <c r="C301" s="0" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F301" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" s="0" t="n">
+        <v>292</v>
+      </c>
+      <c r="C302" s="0" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F302" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" s="0" t="n">
+        <v>293</v>
+      </c>
+      <c r="C303" s="0" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F303" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" s="0" t="n">
+        <v>294</v>
+      </c>
+      <c r="C304" s="0" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F304" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" s="0" t="n">
+        <v>295</v>
+      </c>
+      <c r="C305" s="0" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F305" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" s="0" t="n">
+        <v>296</v>
+      </c>
+      <c r="C306" s="0" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F306" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" s="0" t="n">
+        <v>297</v>
+      </c>
+      <c r="C307" s="0" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F307" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" s="0" t="n">
+        <v>298</v>
+      </c>
+      <c r="C308" s="0" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F308" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" s="0" t="n">
+        <v>299</v>
+      </c>
+      <c r="C309" s="0" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F309" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="C310" s="0" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F310" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" s="0" t="n">
+        <v>301</v>
+      </c>
+      <c r="C311" s="0" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F311" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="C312" s="0" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F312" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" s="0" t="n">
+        <v>303</v>
+      </c>
+      <c r="C313" s="0" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F313" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" s="0" t="n">
+        <v>304</v>
+      </c>
+      <c r="C314" s="0" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F314" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" s="0" t="n">
+        <v>305</v>
+      </c>
+      <c r="C315" s="0" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F315" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" s="0" t="n">
+        <v>306</v>
+      </c>
+      <c r="C316" s="0" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F316" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" s="0" t="n">
+        <v>307</v>
+      </c>
+      <c r="C317" s="0" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F317" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" s="0" t="n">
+        <v>308</v>
+      </c>
+      <c r="C318" s="0" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F318" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" s="0" t="n">
+        <v>309</v>
+      </c>
+      <c r="C319" s="0" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F319" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" s="0" t="n">
+        <v>310</v>
+      </c>
+      <c r="C320" s="0" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F320" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" s="0" t="n">
+        <v>311</v>
+      </c>
+      <c r="C321" s="0" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F321" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" s="0" t="n">
+        <v>312</v>
+      </c>
+      <c r="C322" s="0" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F322" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" s="0" t="n">
+        <v>313</v>
+      </c>
+      <c r="C323" s="0" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F323" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" s="0" t="n">
+        <v>314</v>
+      </c>
+      <c r="C324" s="0" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F324" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" s="0" t="n">
+        <v>315</v>
+      </c>
+      <c r="C325" s="0" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F325" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" s="0" t="n">
+        <v>316</v>
+      </c>
+      <c r="C326" s="0" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F326" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" s="0" t="n">
+        <v>317</v>
+      </c>
+      <c r="C327" s="0" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F327" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" s="0" t="n">
+        <v>318</v>
+      </c>
+      <c r="C328" s="0" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F328" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" s="0" t="n">
+        <v>319</v>
+      </c>
+      <c r="C329" s="0" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F329" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" s="0" t="n">
+        <v>320</v>
+      </c>
+      <c r="C330" s="0" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E330" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F330" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" s="0" t="n">
+        <v>321</v>
+      </c>
+      <c r="C331" s="0" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D331" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F331" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" s="0" t="n">
+        <v>322</v>
+      </c>
+      <c r="C332" s="0" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F332" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" s="0" t="n">
+        <v>323</v>
+      </c>
+      <c r="C333" s="0" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F333" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" s="0" t="n">
+        <v>324</v>
+      </c>
+      <c r="C334" s="0" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F334" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" s="0" t="n">
+        <v>325</v>
+      </c>
+      <c r="C335" s="0" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E335" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F335" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" s="0" t="n">
         <v>326</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="B86" t="n">
-        <v>76</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>第 76 回合</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
+      <c r="C336" s="0" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E336" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F336" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" s="0" t="n">
+        <v>327</v>
+      </c>
+      <c r="C337" s="0" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F337" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" s="0" t="n">
+        <v>328</v>
+      </c>
+      <c r="C338" s="0" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F338" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" s="0" t="n">
+        <v>329</v>
+      </c>
+      <c r="C339" s="0" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F339" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" s="0" t="n">
         <v>330</v>
       </c>
-    </row>
-    <row r="87">
-      <c r="B87" t="n">
-        <v>77</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>第 77 回合</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
+      <c r="C340" s="0" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F340" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" s="0" t="n">
+        <v>331</v>
+      </c>
+      <c r="C341" s="0" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F341" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" s="0" t="n">
+        <v>332</v>
+      </c>
+      <c r="C342" s="0" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F342" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" s="0" t="n">
+        <v>333</v>
+      </c>
+      <c r="C343" s="0" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F343" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" s="0" t="n">
         <v>334</v>
       </c>
-    </row>
-    <row r="88">
-      <c r="B88" t="n">
-        <v>78</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>第 78 回合</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
+      <c r="C344" s="0" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F344" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" s="0" t="n">
+        <v>335</v>
+      </c>
+      <c r="C345" s="0" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F345" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" s="0" t="n">
+        <v>336</v>
+      </c>
+      <c r="C346" s="0" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F346" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" s="0" t="n">
+        <v>337</v>
+      </c>
+      <c r="C347" s="0" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F347" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" s="0" t="n">
         <v>338</v>
       </c>
-    </row>
-    <row r="89">
-      <c r="B89" t="n">
-        <v>79</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>第 79 回合</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
+      <c r="C348" s="0" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F348" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" s="0" t="n">
+        <v>339</v>
+      </c>
+      <c r="C349" s="0" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F349" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" s="0" t="n">
+        <v>340</v>
+      </c>
+      <c r="C350" s="0" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F350" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" s="0" t="n">
+        <v>341</v>
+      </c>
+      <c r="C351" s="0" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F351" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" s="0" t="n">
         <v>342</v>
       </c>
-    </row>
-    <row r="90">
-      <c r="B90" t="n">
-        <v>80</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>第 80 回合</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
+      <c r="C352" s="0" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D352" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F352" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" s="0" t="n">
+        <v>343</v>
+      </c>
+      <c r="C353" s="0" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D353" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F353" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" s="0" t="n">
+        <v>344</v>
+      </c>
+      <c r="C354" s="0" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="D354" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F354" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" s="0" t="n">
+        <v>345</v>
+      </c>
+      <c r="C355" s="0" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F355" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" s="0" t="n">
         <v>346</v>
       </c>
-    </row>
-    <row r="91">
-      <c r="B91" t="n">
-        <v>81</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>第 81 回合</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
+      <c r="C356" s="0" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D356" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F356" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" s="0" t="n">
+        <v>347</v>
+      </c>
+      <c r="C357" s="0" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F357" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" s="0" t="n">
+        <v>348</v>
+      </c>
+      <c r="C358" s="0" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E358" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F358" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" s="0" t="n">
+        <v>349</v>
+      </c>
+      <c r="C359" s="0" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D359" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F359" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" s="0" t="n">
         <v>350</v>
       </c>
-    </row>
-    <row r="92">
-      <c r="B92" t="n">
-        <v>82</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>第 82 回合</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
+      <c r="C360" s="0" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="D360" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F360" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" s="0" t="n">
+        <v>351</v>
+      </c>
+      <c r="C361" s="0" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="D361" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E361" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F361" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" s="0" t="n">
+        <v>352</v>
+      </c>
+      <c r="C362" s="0" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D362" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F362" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" s="0" t="n">
+        <v>353</v>
+      </c>
+      <c r="C363" s="0" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D363" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E363" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F363" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" s="0" t="n">
         <v>354</v>
       </c>
-    </row>
-    <row r="93">
-      <c r="B93" t="n">
-        <v>83</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>第 83 回合</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
+      <c r="C364" s="0" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="D364" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E364" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F364" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="C365" s="0" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="D365" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F365" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" s="0" t="n">
+        <v>356</v>
+      </c>
+      <c r="C366" s="0" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F366" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" s="0" t="n">
+        <v>357</v>
+      </c>
+      <c r="C367" s="0" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E367" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F367" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" s="0" t="n">
         <v>358</v>
       </c>
-    </row>
-    <row r="94">
-      <c r="B94" t="n">
-        <v>84</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>第 84 回合</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
+      <c r="C368" s="0" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="D368" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E368" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F368" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" s="0" t="n">
+        <v>359</v>
+      </c>
+      <c r="C369" s="0" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="D369" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E369" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F369" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="C370" s="0" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D370" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E370" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F370" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" s="0" t="n">
+        <v>361</v>
+      </c>
+      <c r="C371" s="0" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="D371" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E371" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F371" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" s="0" t="n">
         <v>362</v>
       </c>
-    </row>
-    <row r="95">
-      <c r="B95" t="n">
-        <v>85</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>第 85 回合</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
+      <c r="C372" s="0" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D372" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E372" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F372" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" s="0" t="n">
+        <v>363</v>
+      </c>
+      <c r="C373" s="0" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="D373" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E373" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F373" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" s="0" t="n">
+        <v>364</v>
+      </c>
+      <c r="C374" s="0" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D374" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E374" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F374" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" s="0" t="n">
+        <v>365</v>
+      </c>
+      <c r="C375" s="0" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="D375" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E375" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F375" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" s="0" t="n">
         <v>366</v>
       </c>
-    </row>
-    <row r="96">
-      <c r="B96" t="n">
-        <v>86</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>第 86 回合</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
+      <c r="C376" s="0" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="D376" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F376" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" s="0" t="n">
+        <v>367</v>
+      </c>
+      <c r="C377" s="0" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="D377" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E377" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F377" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" s="0" t="n">
+        <v>368</v>
+      </c>
+      <c r="C378" s="0" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="D378" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E378" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F378" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" s="0" t="n">
+        <v>369</v>
+      </c>
+      <c r="C379" s="0" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D379" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F379" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" s="0" t="n">
         <v>370</v>
       </c>
-    </row>
-    <row r="97">
-      <c r="B97" t="n">
-        <v>87</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>第 87 回合</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
+      <c r="C380" s="0" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D380" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F380" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" s="0" t="n">
+        <v>371</v>
+      </c>
+      <c r="C381" s="0" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D381" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E381" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F381" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" s="0" t="n">
+        <v>372</v>
+      </c>
+      <c r="C382" s="0" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D382" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E382" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F382" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" s="0" t="n">
+        <v>373</v>
+      </c>
+      <c r="C383" s="0" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D383" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E383" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F383" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" s="0" t="n">
         <v>374</v>
       </c>
-    </row>
-    <row r="98">
-      <c r="B98" t="n">
-        <v>88</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>第 88 回合</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
+      <c r="C384" s="0" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D384" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E384" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F384" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" s="0" t="n">
+        <v>375</v>
+      </c>
+      <c r="C385" s="0" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D385" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E385" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F385" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" s="0" t="n">
+        <v>376</v>
+      </c>
+      <c r="C386" s="0" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="D386" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E386" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F386" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" s="0" t="n">
+        <v>377</v>
+      </c>
+      <c r="C387" s="0" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D387" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E387" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F387" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" s="0" t="n">
         <v>378</v>
       </c>
-    </row>
-    <row r="99">
-      <c r="B99" t="n">
-        <v>89</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>第 89 回合</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
+      <c r="C388" s="0" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D388" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E388" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F388" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" s="0" t="n">
+        <v>379</v>
+      </c>
+      <c r="C389" s="0" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D389" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E389" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F389" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" s="0" t="n">
+        <v>380</v>
+      </c>
+      <c r="C390" s="0" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D390" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E390" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F390" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" s="0" t="n">
+        <v>381</v>
+      </c>
+      <c r="C391" s="0" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="D391" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E391" s="0" t="inlineStr">
+        <is>
+          <t>第 1/20 波</t>
+        </is>
+      </c>
+      <c r="F391" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" s="0" t="n">
         <v>382</v>
       </c>
-    </row>
-    <row r="100">
-      <c r="B100" t="n">
-        <v>90</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>第 90 回合</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
+      <c r="C392" s="0" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D392" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E392" s="0" t="inlineStr">
+        <is>
+          <t>第 2/20 波</t>
+        </is>
+      </c>
+      <c r="F392" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" s="0" t="n">
+        <v>383</v>
+      </c>
+      <c r="C393" s="0" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="D393" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E393" s="0" t="inlineStr">
+        <is>
+          <t>第 3/20 波</t>
+        </is>
+      </c>
+      <c r="F393" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" s="0" t="n">
+        <v>384</v>
+      </c>
+      <c r="C394" s="0" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="D394" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E394" s="0" t="inlineStr">
+        <is>
+          <t>第 4/20 波</t>
+        </is>
+      </c>
+      <c r="F394" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" s="0" t="n">
+        <v>385</v>
+      </c>
+      <c r="C395" s="0" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="D395" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E395" s="0" t="inlineStr">
+        <is>
+          <t>第 5/20 波</t>
+        </is>
+      </c>
+      <c r="F395" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" s="0" t="n">
         <v>386</v>
       </c>
-    </row>
-    <row r="101">
-      <c r="B101" t="n">
-        <v>91</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>第 91 回合</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
+      <c r="C396" s="0" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="D396" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E396" s="0" t="inlineStr">
+        <is>
+          <t>第 6/20 波</t>
+        </is>
+      </c>
+      <c r="F396" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" s="0" t="n">
+        <v>387</v>
+      </c>
+      <c r="C397" s="0" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="D397" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" s="0" t="inlineStr">
+        <is>
+          <t>第 7/20 波</t>
+        </is>
+      </c>
+      <c r="F397" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" s="0" t="n">
+        <v>388</v>
+      </c>
+      <c r="C398" s="0" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="D398" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E398" s="0" t="inlineStr">
+        <is>
+          <t>第 8/20 波</t>
+        </is>
+      </c>
+      <c r="F398" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" s="0" t="n">
+        <v>389</v>
+      </c>
+      <c r="C399" s="0" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="D399" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E399" s="0" t="inlineStr">
+        <is>
+          <t>第 9/20 波</t>
+        </is>
+      </c>
+      <c r="F399" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" s="0" t="n">
         <v>390</v>
       </c>
-    </row>
-    <row r="102">
-      <c r="B102" t="n">
-        <v>92</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>第 92 回合</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
+      <c r="C400" s="0" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="D400" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E400" s="0" t="inlineStr">
+        <is>
+          <t>第 10/20 波</t>
+        </is>
+      </c>
+      <c r="F400" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" s="0" t="n">
+        <v>391</v>
+      </c>
+      <c r="C401" s="0" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="D401" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E401" s="0" t="inlineStr">
+        <is>
+          <t>第 11/20 波</t>
+        </is>
+      </c>
+      <c r="F401" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" s="0" t="n">
+        <v>392</v>
+      </c>
+      <c r="C402" s="0" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="D402" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E402" s="0" t="inlineStr">
+        <is>
+          <t>第 12/20 波</t>
+        </is>
+      </c>
+      <c r="F402" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" s="0" t="n">
+        <v>393</v>
+      </c>
+      <c r="C403" s="0" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="D403" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E403" s="0" t="inlineStr">
+        <is>
+          <t>第 13/20 波</t>
+        </is>
+      </c>
+      <c r="F403" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" s="0" t="n">
         <v>394</v>
       </c>
-    </row>
-    <row r="103">
-      <c r="B103" t="n">
-        <v>93</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>第 93 回合</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
+      <c r="C404" s="0" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="D404" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" s="0" t="inlineStr">
+        <is>
+          <t>第 14/20 波</t>
+        </is>
+      </c>
+      <c r="F404" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" s="0" t="n">
+        <v>395</v>
+      </c>
+      <c r="C405" s="0" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="D405" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E405" s="0" t="inlineStr">
+        <is>
+          <t>第 15/20 波</t>
+        </is>
+      </c>
+      <c r="F405" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" s="0" t="n">
+        <v>396</v>
+      </c>
+      <c r="C406" s="0" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="D406" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E406" s="0" t="inlineStr">
+        <is>
+          <t>第 16/20 波</t>
+        </is>
+      </c>
+      <c r="F406" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" s="0" t="n">
+        <v>397</v>
+      </c>
+      <c r="C407" s="0" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="D407" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" s="0" t="inlineStr">
+        <is>
+          <t>第 17/20 波</t>
+        </is>
+      </c>
+      <c r="F407" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" s="0" t="n">
         <v>398</v>
       </c>
-    </row>
-    <row r="104">
-      <c r="B104" t="n">
-        <v>94</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>第 94 回合</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" t="n">
-        <v>95</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>第 95 回合</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" t="n">
-        <v>96</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>第 96 回合</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" t="n">
-        <v>97</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>第 97 回合</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" t="n">
-        <v>98</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>第 98 回合</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" t="n">
-        <v>99</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>第 99 回合</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" t="n">
-        <v>100</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>第 100 回合</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>426</v>
+      <c r="C408" s="0" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E408" s="0" t="inlineStr">
+        <is>
+          <t>第 18/20 波</t>
+        </is>
+      </c>
+      <c r="F408" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" s="0" t="n">
+        <v>399</v>
+      </c>
+      <c r="C409" s="0" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="D409" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" s="0" t="inlineStr">
+        <is>
+          <t>第 19/20 波</t>
+        </is>
+      </c>
+      <c r="F409" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="C410" s="0" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D410" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" s="0" t="inlineStr">
+        <is>
+          <t>第 20/20 波</t>
+        </is>
+      </c>
+      <c r="F410" s="0" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/RoundData.xlsx
+++ b/Luban/Config/Datas/RoundData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="F4" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="F5" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F6" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="1" s="2">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="F12" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L12" s="13" t="n"/>
       <c r="M12" s="13" t="n"/>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="F13" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L13" s="13" t="n"/>
       <c r="M13" s="13" t="n"/>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="F14" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="F15" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L15" s="13" t="n"/>
       <c r="M15" s="13" t="n"/>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="F16" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" s="1">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="F17" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" s="1">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F18" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" s="1">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F19" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" s="1">
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="F20" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" s="1">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="F21" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F22" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="F23" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="F24" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="F25" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="F26" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="F27" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="F28" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="F29" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="F30" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="F31" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="F32" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="F33" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F34" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="F35" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="F36" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="F37" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F38" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F39" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="F40" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="F41" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="F42" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="F43" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44">
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="F44" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="F45" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="F46" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="F47" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="F48" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="F49" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="F50" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="F51" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F52" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="F53" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="F54" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="F55" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F56" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="F57" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="F58" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="F59" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="F60" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="F61" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62">
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="F62" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="F63" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="F64" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="F65" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="F66" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="F67" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68">
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="F68" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="F69" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="F70" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="F71" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="F72" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="F73" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="F74" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="F75" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="F76" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="F77" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="F78" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F79" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="F80" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="F81" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="F82" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="F83" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84">
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="F84" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="F85" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="F86" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="F87" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="F88" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89">
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="F89" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90">
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="F90" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="F91" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="F92" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F93" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="F94" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F95" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="F96" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F97" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98">
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="F98" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99">
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="F99" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100">
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="F100" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="F101" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102">
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="F102" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103">
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="F103" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104">
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="F104" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F105" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="F106" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107">
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="F107" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="108">
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="F108" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="F109" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="110">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="F110" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="111">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="F111" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112">
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="F112" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="F113" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="114">
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="F114" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115">
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="F115" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="116">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="F116" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="117">
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="F117" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="118">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="F118" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="119">
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F119" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="120">
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="F120" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="121">
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="F121" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="F122" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="F123" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124">
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="F124" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="F125" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="F126" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="127">
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="F127" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="128">
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="F128" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="F129" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130">
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="F130" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="131">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="F131" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="132">
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="F132" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="133">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="F133" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134">
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="F134" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="135">
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="F135" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="136">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="F136" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="F137" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="138">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F138" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="139">
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="F139" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="140">
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="F140" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="141">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="F141" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="142">
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="F142" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="143">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="F143" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="144">
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="F144" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="145">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="F145" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="146">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="F146" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147">
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="F147" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="148">
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="F148" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="149">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="F149" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="150">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="F150" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="151">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="F151" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="152">
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="F152" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="153">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F153" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154">
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="F154" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="155">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="F155" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="156">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="F156" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="157">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="F157" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="158">
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="F158" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="159">
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="F159" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="160">
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="F160" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="161">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="F161" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="162">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="F162" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="163">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="F163" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="164">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="F164" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="165">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="F165" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="166">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="F166" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="167">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="F167" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="168">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="F168" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="169">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="F169" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="170">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="F170" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="171">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="F171" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="172">
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="F172" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="173">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="F173" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174">
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="F174" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="175">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="F175" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="176">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="F176" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="177">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="F177" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="178">
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="F178" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="179">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="F179" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="180">
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="F180" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="181">
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="F181" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="F182" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="183">
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="F183" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="184">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="F184" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="185">
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="F185" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="186">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="F186" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="187">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="F187" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="188">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="F188" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="F189" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="190">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="F190" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="191">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="F191" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="192">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="F192" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="193">
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="F193" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="194">
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="F194" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="195">
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="F195" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="196">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="F196" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="197">
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="F197" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="198">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="F198" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="199">
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="F199" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="200">
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="F200" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="201">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="F201" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="202">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="F202" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="203">
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="F203" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="204">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="F204" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="205">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="F205" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="206">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="F206" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="207">
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="F207" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="208">
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="F208" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="209">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="F209" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="210">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="F210" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="211">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="F211" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="212">
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="F212" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="213">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="F213" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="214">
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="F214" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="215">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="F215" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="216">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="F216" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="217">
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="F217" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="218">
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="F218" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="219">
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="F219" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="220">
@@ -5850,7 +5850,7 @@
         </is>
       </c>
       <c r="F220" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="221">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="F221" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="222">
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="F222" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="223">
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="F223" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="224">
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="F224" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="225">
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="F225" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="226">
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="F226" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="227">
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="F227" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="228">
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="F228" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="229">
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="F229" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="230">
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="F230" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="231">
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="F231" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="232">
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="F232" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="233">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="F233" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="234">
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="F234" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="235">
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="F235" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="236">
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="F236" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="237">
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="F237" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="238">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="F238" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="239">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="F239" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="240">
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="F240" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="241">
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="F241" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="242">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="F242" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="243">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="F243" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="244">
@@ -6354,7 +6354,7 @@
         </is>
       </c>
       <c r="F244" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="245">
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="F245" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="246">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="F246" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="247">
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="F247" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="248">
@@ -6438,7 +6438,7 @@
         </is>
       </c>
       <c r="F248" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="249">
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="F249" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="250">
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="F250" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="251">
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="F251" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="252">
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="F252" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="253">
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="F253" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="254">
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="F254" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="255">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="F255" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="256">
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="F256" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="257">
@@ -6627,7 +6627,7 @@
         </is>
       </c>
       <c r="F257" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="258">
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="F258" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="259">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="F259" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="260">
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="F260" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="261">
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="F261" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="262">
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="F262" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="263">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="F263" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="264">
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="F264" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="265">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="F265" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="266">
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="F266" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="267">
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="F267" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="268">
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="F268" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="269">
@@ -6879,7 +6879,7 @@
         </is>
       </c>
       <c r="F269" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="270">
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="F270" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="271">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="F271" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="272">
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="F272" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="273">
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="F273" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="274">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="F274" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="275">
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="F275" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="276">
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="F276" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="277">
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="F277" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="278">
@@ -7068,7 +7068,7 @@
         </is>
       </c>
       <c r="F278" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="279">
@@ -7089,7 +7089,7 @@
         </is>
       </c>
       <c r="F279" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="280">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="F280" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="281">
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="F281" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="282">
@@ -7152,7 +7152,7 @@
         </is>
       </c>
       <c r="F282" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="283">
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="F283" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="284">
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="F284" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="285">
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="F285" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="286">
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="F286" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="287">
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="F287" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="288">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="F288" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="289">
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="F289" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="290">
@@ -7320,7 +7320,7 @@
         </is>
       </c>
       <c r="F290" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="291">
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="F291" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="292">
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="F292" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="293">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="F293" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="294">
@@ -7404,7 +7404,7 @@
         </is>
       </c>
       <c r="F294" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="295">
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="F295" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="296">
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="F296" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="297">
@@ -7467,7 +7467,7 @@
         </is>
       </c>
       <c r="F297" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="298">
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="F298" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="299">
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="F299" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="300">
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="F300" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="301">
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="F301" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="302">
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="F302" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="303">
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="F303" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="304">
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="F304" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="305">
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="F305" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="306">
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="F306" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="307">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="F307" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="308">
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="F308" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="309">
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="F309" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="310">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="F310" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="311">
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="F311" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="312">
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="F312" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="313">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="F313" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="314">
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="F314" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="315">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="F315" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="316">
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="F316" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="317">
@@ -7887,7 +7887,7 @@
         </is>
       </c>
       <c r="F317" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="318">
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="F318" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="319">
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="F319" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="320">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="F320" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="321">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="F321" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="322">
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="F322" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="323">
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="F323" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="324">
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="F324" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="325">
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="F325" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="326">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="F326" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="327">
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="F327" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="328">
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="F328" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="329">
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="F329" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="330">
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="F330" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="331">
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="F331" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="332">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="F332" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="333">
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F333" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="334">
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="F334" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="335">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="F335" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="336">
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="F336" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="337">
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="F337" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="338">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="F338" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="339">
@@ -8349,7 +8349,7 @@
         </is>
       </c>
       <c r="F339" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="340">
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="F340" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="341">
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="F341" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="342">
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="F342" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="343">
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="F343" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="344">
@@ -8454,7 +8454,7 @@
         </is>
       </c>
       <c r="F344" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="345">
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="F345" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="346">
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="F346" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="347">
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F347" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="348">
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="F348" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="349">
@@ -8559,7 +8559,7 @@
         </is>
       </c>
       <c r="F349" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350">
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="F350" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="351">
@@ -8601,7 +8601,7 @@
         </is>
       </c>
       <c r="F351" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="352">
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="F352" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="353">
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="F353" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="354">
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="F354" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="355">
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="F355" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="356">
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="F356" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="357">
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="F357" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="358">
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="F358" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="359">
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="F359" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="360">
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="F360" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="361">
@@ -8811,7 +8811,7 @@
         </is>
       </c>
       <c r="F361" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="362">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="F362" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="363">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="F363" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="364">
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="F364" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="365">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="F365" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="366">
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="F366" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="367">
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="F367" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="368">
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="F368" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="369">
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="F369" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="370">
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="F370" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="371">
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="F371" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="372">
@@ -9042,7 +9042,7 @@
         </is>
       </c>
       <c r="F372" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="373">
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="F373" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="374">
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="F374" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="375">
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="F375" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="376">
@@ -9126,7 +9126,7 @@
         </is>
       </c>
       <c r="F376" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="377">
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="F377" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="378">
@@ -9168,7 +9168,7 @@
         </is>
       </c>
       <c r="F378" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="379">
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="F379" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="380">
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="F380" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="381">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="F381" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="382">
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="F382" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="383">
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="F383" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="384">
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="F384" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="385">
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="F385" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="386">
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="F386" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="387">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="F387" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="388">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="F388" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="389">
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="F389" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="390">
@@ -9420,7 +9420,7 @@
         </is>
       </c>
       <c r="F390" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="391">
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="F391" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="392">
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="F392" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="393">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="F393" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="394">
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="F394" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="395">
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="F395" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="396">
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="F396" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="397">
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="F397" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="398">
@@ -9588,7 +9588,7 @@
         </is>
       </c>
       <c r="F398" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="399">
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="F399" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="400">
@@ -9630,7 +9630,7 @@
         </is>
       </c>
       <c r="F400" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="401">
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="F401" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="402">
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="F402" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="403">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="F403" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="404">
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="F404" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="405">
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="F405" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="406">
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="F406" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="407">
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="F407" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="408">
@@ -9798,7 +9798,7 @@
         </is>
       </c>
       <c r="F408" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="409">
@@ -9819,7 +9819,7 @@
         </is>
       </c>
       <c r="F409" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="410">
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="F410" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="411">
@@ -9861,7 +9861,7 @@
         </is>
       </c>
       <c r="F411" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="412">
@@ -9882,7 +9882,7 @@
         </is>
       </c>
       <c r="F412" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="413">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="F413" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="414">
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="F414" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="415">
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="F415" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="416">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="F416" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="417">
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="F417" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="418">
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="F418" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="419">
@@ -10029,7 +10029,7 @@
         </is>
       </c>
       <c r="F419" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="420">
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="F420" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="421">
@@ -10071,7 +10071,7 @@
         </is>
       </c>
       <c r="F421" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="422">
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="F422" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="423">
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="F423" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="424">
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="F424" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="425">
@@ -10155,7 +10155,7 @@
         </is>
       </c>
       <c r="F425" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="426">
@@ -10176,7 +10176,7 @@
         </is>
       </c>
       <c r="F426" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="427">
@@ -10197,7 +10197,7 @@
         </is>
       </c>
       <c r="F427" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="428">
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="F428" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="429">
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="F429" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="430">
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="F430" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="431">
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="F431" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="432">
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="F432" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="433">
@@ -10323,7 +10323,7 @@
         </is>
       </c>
       <c r="F433" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="434">
@@ -10344,7 +10344,7 @@
         </is>
       </c>
       <c r="F434" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="435">
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="F435" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="436">
@@ -10386,7 +10386,7 @@
         </is>
       </c>
       <c r="F436" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="437">
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="F437" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="438">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="F438" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="439">
@@ -10449,7 +10449,7 @@
         </is>
       </c>
       <c r="F439" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="440">
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="F440" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="441">
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="F441" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="442">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="F442" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="443">
@@ -10533,7 +10533,7 @@
         </is>
       </c>
       <c r="F443" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="444">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="F444" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="445">
@@ -10575,7 +10575,7 @@
         </is>
       </c>
       <c r="F445" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="446">
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="F446" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="447">
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="F447" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="448">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="F448" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="449">
@@ -10659,7 +10659,7 @@
         </is>
       </c>
       <c r="F449" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="450">
@@ -10680,7 +10680,7 @@
         </is>
       </c>
       <c r="F450" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="451">
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="F451" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="452">
@@ -10722,7 +10722,7 @@
         </is>
       </c>
       <c r="F452" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="453">
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="F453" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="454">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="F454" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="455">
@@ -10785,7 +10785,7 @@
         </is>
       </c>
       <c r="F455" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="456">
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="F456" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="457">
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="F457" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="458">
@@ -10848,7 +10848,7 @@
         </is>
       </c>
       <c r="F458" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="459">
@@ -10869,7 +10869,7 @@
         </is>
       </c>
       <c r="F459" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="460">
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="F460" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="461">
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="F461" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="462">
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="F462" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="463">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="F463" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="464">
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="F464" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="465">
@@ -10995,7 +10995,7 @@
         </is>
       </c>
       <c r="F465" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="466">
@@ -11016,7 +11016,7 @@
         </is>
       </c>
       <c r="F466" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="467">
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="F467" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="468">
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="F468" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="469">
@@ -11079,7 +11079,7 @@
         </is>
       </c>
       <c r="F469" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="470">
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="F470" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="471">
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="F471" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="472">
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="F472" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="473">
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="F473" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="474">
@@ -11184,7 +11184,7 @@
         </is>
       </c>
       <c r="F474" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="475">
@@ -11205,7 +11205,7 @@
         </is>
       </c>
       <c r="F475" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="476">
@@ -11226,7 +11226,7 @@
         </is>
       </c>
       <c r="F476" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="477">
@@ -11247,7 +11247,7 @@
         </is>
       </c>
       <c r="F477" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="478">
@@ -11268,7 +11268,7 @@
         </is>
       </c>
       <c r="F478" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="479">
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="F479" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="480">
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="F480" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="481">
@@ -11331,7 +11331,7 @@
         </is>
       </c>
       <c r="F481" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="482">
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="F482" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="483">
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="F483" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="484">
@@ -11394,7 +11394,7 @@
         </is>
       </c>
       <c r="F484" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="485">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="F485" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="486">
@@ -11436,7 +11436,7 @@
         </is>
       </c>
       <c r="F486" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="487">
@@ -11457,7 +11457,7 @@
         </is>
       </c>
       <c r="F487" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="488">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="F488" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="489">
@@ -11499,7 +11499,7 @@
         </is>
       </c>
       <c r="F489" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="490">
@@ -11520,7 +11520,7 @@
         </is>
       </c>
       <c r="F490" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="491">
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="F491" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="492">
@@ -11562,7 +11562,7 @@
         </is>
       </c>
       <c r="F492" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="493">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="F493" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="494">
@@ -11604,7 +11604,7 @@
         </is>
       </c>
       <c r="F494" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="495">
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="F495" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="496">
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="F496" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="497">
@@ -11667,7 +11667,7 @@
         </is>
       </c>
       <c r="F497" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="498">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="F498" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="499">
@@ -11709,7 +11709,7 @@
         </is>
       </c>
       <c r="F499" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="500">
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="F500" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="501">
@@ -11751,7 +11751,7 @@
         </is>
       </c>
       <c r="F501" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="502">
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="F502" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="503">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="F503" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="504">
@@ -11814,7 +11814,7 @@
         </is>
       </c>
       <c r="F504" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="505">
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="F505" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="506">
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="F506" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="507">
@@ -11877,7 +11877,7 @@
         </is>
       </c>
       <c r="F507" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="508">
@@ -11898,7 +11898,7 @@
         </is>
       </c>
       <c r="F508" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="509">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="F509" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="510">
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="F510" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="511">
@@ -11961,7 +11961,7 @@
         </is>
       </c>
       <c r="F511" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="512">
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="F512" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="513">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="F513" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="514">
@@ -12024,7 +12024,7 @@
         </is>
       </c>
       <c r="F514" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="515">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="F515" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="516">
@@ -12066,7 +12066,7 @@
         </is>
       </c>
       <c r="F516" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="517">
@@ -12087,7 +12087,7 @@
         </is>
       </c>
       <c r="F517" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="518">
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="F518" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="519">
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="F519" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="520">
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="F520" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="521">
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="F521" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="522">
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="F522" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="523">
@@ -12213,7 +12213,7 @@
         </is>
       </c>
       <c r="F523" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="524">
@@ -12234,7 +12234,7 @@
         </is>
       </c>
       <c r="F524" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="525">
@@ -12255,7 +12255,7 @@
         </is>
       </c>
       <c r="F525" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="526">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="F526" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="527">
@@ -12297,7 +12297,7 @@
         </is>
       </c>
       <c r="F527" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="528">
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="F528" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="529">
@@ -12339,7 +12339,7 @@
         </is>
       </c>
       <c r="F529" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="530">
@@ -12360,7 +12360,7 @@
         </is>
       </c>
       <c r="F530" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="531">
@@ -12381,7 +12381,7 @@
         </is>
       </c>
       <c r="F531" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="532">
@@ -12402,7 +12402,7 @@
         </is>
       </c>
       <c r="F532" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="533">
@@ -12423,7 +12423,7 @@
         </is>
       </c>
       <c r="F533" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="534">
@@ -12444,7 +12444,7 @@
         </is>
       </c>
       <c r="F534" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="535">
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="F535" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="536">
@@ -12486,7 +12486,7 @@
         </is>
       </c>
       <c r="F536" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="537">
@@ -12507,7 +12507,7 @@
         </is>
       </c>
       <c r="F537" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="538">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="F538" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="539">
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="F539" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="540">
@@ -12570,7 +12570,7 @@
         </is>
       </c>
       <c r="F540" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="541">
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="F541" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="542">
@@ -12612,7 +12612,7 @@
         </is>
       </c>
       <c r="F542" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="543">
@@ -12633,7 +12633,7 @@
         </is>
       </c>
       <c r="F543" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="544">
@@ -12654,7 +12654,7 @@
         </is>
       </c>
       <c r="F544" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="545">
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="F545" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="546">
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="F546" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="547">
@@ -12717,7 +12717,7 @@
         </is>
       </c>
       <c r="F547" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="548">
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="F548" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="549">
@@ -12759,7 +12759,7 @@
         </is>
       </c>
       <c r="F549" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="550">
@@ -12780,7 +12780,7 @@
         </is>
       </c>
       <c r="F550" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="551">
@@ -12801,7 +12801,7 @@
         </is>
       </c>
       <c r="F551" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="552">
@@ -12822,7 +12822,7 @@
         </is>
       </c>
       <c r="F552" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="553">
@@ -12843,7 +12843,7 @@
         </is>
       </c>
       <c r="F553" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="554">
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="F554" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="555">
@@ -12885,7 +12885,7 @@
         </is>
       </c>
       <c r="F555" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="556">
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="F556" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="557">
@@ -12927,7 +12927,7 @@
         </is>
       </c>
       <c r="F557" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="558">
@@ -12948,7 +12948,7 @@
         </is>
       </c>
       <c r="F558" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="559">
@@ -12969,7 +12969,7 @@
         </is>
       </c>
       <c r="F559" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="560">
@@ -12990,7 +12990,7 @@
         </is>
       </c>
       <c r="F560" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="561">
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="F561" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="562">
@@ -13032,7 +13032,7 @@
         </is>
       </c>
       <c r="F562" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="563">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="F563" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="564">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="F564" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="565">
@@ -13095,7 +13095,7 @@
         </is>
       </c>
       <c r="F565" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="566">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="F566" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="567">
@@ -13137,7 +13137,7 @@
         </is>
       </c>
       <c r="F567" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="568">
@@ -13158,7 +13158,7 @@
         </is>
       </c>
       <c r="F568" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="569">
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="F569" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="570">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="F570" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="571">
@@ -13221,7 +13221,7 @@
         </is>
       </c>
       <c r="F571" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="572">
@@ -13242,7 +13242,7 @@
         </is>
       </c>
       <c r="F572" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="573">
@@ -13263,7 +13263,7 @@
         </is>
       </c>
       <c r="F573" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="574">
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="F574" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="575">
@@ -13305,7 +13305,7 @@
         </is>
       </c>
       <c r="F575" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="576">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="F576" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="577">
@@ -13347,7 +13347,7 @@
         </is>
       </c>
       <c r="F577" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="578">
@@ -13368,7 +13368,7 @@
         </is>
       </c>
       <c r="F578" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="579">
@@ -13389,7 +13389,7 @@
         </is>
       </c>
       <c r="F579" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="580">
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="F580" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="581">
@@ -13431,7 +13431,7 @@
         </is>
       </c>
       <c r="F581" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="582">
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="F582" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="583">
@@ -13473,7 +13473,7 @@
         </is>
       </c>
       <c r="F583" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="584">
@@ -13494,7 +13494,7 @@
         </is>
       </c>
       <c r="F584" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="585">
@@ -13515,7 +13515,7 @@
         </is>
       </c>
       <c r="F585" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="586">
@@ -13536,7 +13536,7 @@
         </is>
       </c>
       <c r="F586" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="587">
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F587" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="588">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="F588" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="589">
@@ -13599,7 +13599,7 @@
         </is>
       </c>
       <c r="F589" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="590">
@@ -13620,7 +13620,7 @@
         </is>
       </c>
       <c r="F590" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="591">
@@ -13641,7 +13641,7 @@
         </is>
       </c>
       <c r="F591" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="592">
@@ -13662,7 +13662,7 @@
         </is>
       </c>
       <c r="F592" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="593">
@@ -13683,7 +13683,7 @@
         </is>
       </c>
       <c r="F593" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="594">
@@ -13704,7 +13704,7 @@
         </is>
       </c>
       <c r="F594" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="595">
@@ -13725,7 +13725,7 @@
         </is>
       </c>
       <c r="F595" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="596">
@@ -13746,7 +13746,7 @@
         </is>
       </c>
       <c r="F596" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="597">
@@ -13767,7 +13767,7 @@
         </is>
       </c>
       <c r="F597" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="598">
@@ -13788,7 +13788,7 @@
         </is>
       </c>
       <c r="F598" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="599">
@@ -13809,7 +13809,7 @@
         </is>
       </c>
       <c r="F599" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="600">
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="F600" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="601">
@@ -13851,7 +13851,7 @@
         </is>
       </c>
       <c r="F601" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="602">
@@ -13872,7 +13872,7 @@
         </is>
       </c>
       <c r="F602" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="603">
@@ -13893,7 +13893,7 @@
         </is>
       </c>
       <c r="F603" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="604">
@@ -13914,7 +13914,7 @@
         </is>
       </c>
       <c r="F604" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="605">
@@ -13935,7 +13935,7 @@
         </is>
       </c>
       <c r="F605" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="606">
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="F606" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="607">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="F607" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="608">
@@ -13998,7 +13998,7 @@
         </is>
       </c>
       <c r="F608" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="609">
@@ -14019,7 +14019,7 @@
         </is>
       </c>
       <c r="F609" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="610">
@@ -14040,7 +14040,7 @@
         </is>
       </c>
       <c r="F610" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="611">
@@ -14061,7 +14061,7 @@
         </is>
       </c>
       <c r="F611" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="612">
@@ -14082,7 +14082,7 @@
         </is>
       </c>
       <c r="F612" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="613">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="F613" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="614">
@@ -14124,7 +14124,7 @@
         </is>
       </c>
       <c r="F614" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="615">
@@ -14145,7 +14145,7 @@
         </is>
       </c>
       <c r="F615" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="616">
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="F616" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="617">
@@ -14187,7 +14187,7 @@
         </is>
       </c>
       <c r="F617" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="618">
@@ -14208,7 +14208,7 @@
         </is>
       </c>
       <c r="F618" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="619">
@@ -14229,7 +14229,7 @@
         </is>
       </c>
       <c r="F619" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="620">
@@ -14250,7 +14250,7 @@
         </is>
       </c>
       <c r="F620" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="621">
@@ -14271,7 +14271,7 @@
         </is>
       </c>
       <c r="F621" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="622">
@@ -14292,7 +14292,7 @@
         </is>
       </c>
       <c r="F622" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="623">
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="F623" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="624">
@@ -14334,7 +14334,7 @@
         </is>
       </c>
       <c r="F624" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="625">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="F625" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="626">
@@ -14376,7 +14376,7 @@
         </is>
       </c>
       <c r="F626" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="627">
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="F627" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="628">
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="F628" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="629">
@@ -14439,7 +14439,7 @@
         </is>
       </c>
       <c r="F629" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="630">
@@ -14460,7 +14460,7 @@
         </is>
       </c>
       <c r="F630" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="631">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="F631" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="632">
@@ -14502,7 +14502,7 @@
         </is>
       </c>
       <c r="F632" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="633">
@@ -14523,7 +14523,7 @@
         </is>
       </c>
       <c r="F633" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="634">
@@ -14544,7 +14544,7 @@
         </is>
       </c>
       <c r="F634" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="635">
@@ -14565,7 +14565,7 @@
         </is>
       </c>
       <c r="F635" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="636">
@@ -14586,7 +14586,7 @@
         </is>
       </c>
       <c r="F636" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="637">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="F637" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="638">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="F638" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="639">
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="F639" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="640">
@@ -14670,7 +14670,7 @@
         </is>
       </c>
       <c r="F640" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="641">
@@ -14691,7 +14691,7 @@
         </is>
       </c>
       <c r="F641" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="642">
@@ -14712,7 +14712,7 @@
         </is>
       </c>
       <c r="F642" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="643">
@@ -14733,7 +14733,7 @@
         </is>
       </c>
       <c r="F643" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="644">
@@ -14754,7 +14754,7 @@
         </is>
       </c>
       <c r="F644" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="645">
@@ -14775,7 +14775,7 @@
         </is>
       </c>
       <c r="F645" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="646">
@@ -14796,7 +14796,7 @@
         </is>
       </c>
       <c r="F646" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="647">
@@ -14817,7 +14817,7 @@
         </is>
       </c>
       <c r="F647" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="648">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="F648" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="649">
@@ -14859,7 +14859,7 @@
         </is>
       </c>
       <c r="F649" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="650">
@@ -14880,7 +14880,7 @@
         </is>
       </c>
       <c r="F650" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="651">
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="F651" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="652">
@@ -14922,7 +14922,7 @@
         </is>
       </c>
       <c r="F652" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="653">
@@ -14943,7 +14943,7 @@
         </is>
       </c>
       <c r="F653" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="654">
@@ -14964,7 +14964,7 @@
         </is>
       </c>
       <c r="F654" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="655">
@@ -14985,7 +14985,7 @@
         </is>
       </c>
       <c r="F655" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="656">
@@ -15006,7 +15006,7 @@
         </is>
       </c>
       <c r="F656" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="657">
@@ -15027,7 +15027,7 @@
         </is>
       </c>
       <c r="F657" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="658">
@@ -15048,7 +15048,7 @@
         </is>
       </c>
       <c r="F658" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="659">
@@ -15069,7 +15069,7 @@
         </is>
       </c>
       <c r="F659" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="660">
@@ -15090,7 +15090,7 @@
         </is>
       </c>
       <c r="F660" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="661">
@@ -15111,7 +15111,7 @@
         </is>
       </c>
       <c r="F661" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="662">
@@ -15132,7 +15132,7 @@
         </is>
       </c>
       <c r="F662" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="663">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="F663" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="664">
@@ -15174,7 +15174,7 @@
         </is>
       </c>
       <c r="F664" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="665">
@@ -15195,7 +15195,7 @@
         </is>
       </c>
       <c r="F665" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="666">
@@ -15216,7 +15216,7 @@
         </is>
       </c>
       <c r="F666" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="667">
@@ -15237,7 +15237,7 @@
         </is>
       </c>
       <c r="F667" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="668">
@@ -15258,7 +15258,7 @@
         </is>
       </c>
       <c r="F668" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="669">
@@ -15279,7 +15279,7 @@
         </is>
       </c>
       <c r="F669" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="670">
@@ -15300,7 +15300,7 @@
         </is>
       </c>
       <c r="F670" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="671">
@@ -15321,7 +15321,7 @@
         </is>
       </c>
       <c r="F671" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="672">
@@ -15342,7 +15342,7 @@
         </is>
       </c>
       <c r="F672" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="673">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="F673" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="674">
@@ -15384,7 +15384,7 @@
         </is>
       </c>
       <c r="F674" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="675">
@@ -15405,7 +15405,7 @@
         </is>
       </c>
       <c r="F675" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="676">
@@ -15426,7 +15426,7 @@
         </is>
       </c>
       <c r="F676" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="677">
@@ -15447,7 +15447,7 @@
         </is>
       </c>
       <c r="F677" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="678">
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="F678" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="679">
@@ -15489,7 +15489,7 @@
         </is>
       </c>
       <c r="F679" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="680">
@@ -15510,7 +15510,7 @@
         </is>
       </c>
       <c r="F680" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="681">
@@ -15531,7 +15531,7 @@
         </is>
       </c>
       <c r="F681" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="682">
@@ -15552,7 +15552,7 @@
         </is>
       </c>
       <c r="F682" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="683">
@@ -15573,7 +15573,7 @@
         </is>
       </c>
       <c r="F683" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="684">
@@ -15594,7 +15594,7 @@
         </is>
       </c>
       <c r="F684" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="685">
@@ -15615,7 +15615,7 @@
         </is>
       </c>
       <c r="F685" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="686">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="F686" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="687">
@@ -15657,7 +15657,7 @@
         </is>
       </c>
       <c r="F687" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="688">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="F688" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="689">
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="F689" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="690">
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="F690" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="691">
@@ -15741,7 +15741,7 @@
         </is>
       </c>
       <c r="F691" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="692">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="F692" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="693">
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="F693" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="694">
@@ -15804,7 +15804,7 @@
         </is>
       </c>
       <c r="F694" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="695">
@@ -15825,7 +15825,7 @@
         </is>
       </c>
       <c r="F695" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="696">
@@ -15846,7 +15846,7 @@
         </is>
       </c>
       <c r="F696" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="697">
@@ -15867,7 +15867,7 @@
         </is>
       </c>
       <c r="F697" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="698">
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="F698" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="699">
@@ -15909,7 +15909,7 @@
         </is>
       </c>
       <c r="F699" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="700">
@@ -15930,7 +15930,7 @@
         </is>
       </c>
       <c r="F700" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="701">
@@ -15951,7 +15951,7 @@
         </is>
       </c>
       <c r="F701" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="702">
@@ -15972,7 +15972,7 @@
         </is>
       </c>
       <c r="F702" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="703">
@@ -15993,7 +15993,7 @@
         </is>
       </c>
       <c r="F703" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="704">
@@ -16014,7 +16014,7 @@
         </is>
       </c>
       <c r="F704" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="705">
@@ -16035,7 +16035,7 @@
         </is>
       </c>
       <c r="F705" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="706">
@@ -16056,7 +16056,7 @@
         </is>
       </c>
       <c r="F706" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="707">
@@ -16077,7 +16077,7 @@
         </is>
       </c>
       <c r="F707" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="708">
@@ -16098,7 +16098,7 @@
         </is>
       </c>
       <c r="F708" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="709">
@@ -16119,7 +16119,7 @@
         </is>
       </c>
       <c r="F709" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="710">
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="F710" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="711">
@@ -16161,7 +16161,7 @@
         </is>
       </c>
       <c r="F711" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="712">
@@ -16182,7 +16182,7 @@
         </is>
       </c>
       <c r="F712" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="713">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="F713" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="714">
@@ -16224,7 +16224,7 @@
         </is>
       </c>
       <c r="F714" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="715">
@@ -16245,7 +16245,7 @@
         </is>
       </c>
       <c r="F715" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="716">
@@ -16266,7 +16266,7 @@
         </is>
       </c>
       <c r="F716" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="717">
@@ -16287,7 +16287,7 @@
         </is>
       </c>
       <c r="F717" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="718">
@@ -16308,7 +16308,7 @@
         </is>
       </c>
       <c r="F718" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="719">
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="F719" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="720">
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="F720" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="721">
@@ -16371,7 +16371,7 @@
         </is>
       </c>
       <c r="F721" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="722">
@@ -16392,7 +16392,7 @@
         </is>
       </c>
       <c r="F722" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="723">
@@ -16413,7 +16413,7 @@
         </is>
       </c>
       <c r="F723" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="724">
@@ -16434,7 +16434,7 @@
         </is>
       </c>
       <c r="F724" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="725">
@@ -16455,7 +16455,7 @@
         </is>
       </c>
       <c r="F725" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="726">
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="F726" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="727">
@@ -16497,7 +16497,7 @@
         </is>
       </c>
       <c r="F727" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="728">
@@ -16518,7 +16518,7 @@
         </is>
       </c>
       <c r="F728" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="729">
@@ -16539,7 +16539,7 @@
         </is>
       </c>
       <c r="F729" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="730">
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="F730" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="731">
@@ -16581,7 +16581,7 @@
         </is>
       </c>
       <c r="F731" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="732">
@@ -16602,7 +16602,7 @@
         </is>
       </c>
       <c r="F732" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="733">
@@ -16623,7 +16623,7 @@
         </is>
       </c>
       <c r="F733" s="0" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="734">
@@ -16644,7 +16644,7 @@
         </is>
       </c>
       <c r="F734" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="735">
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="F735" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="736">
@@ -16686,7 +16686,7 @@
         </is>
       </c>
       <c r="F736" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="737">
@@ -16707,7 +16707,7 @@
         </is>
       </c>
       <c r="F737" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="738">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="F738" s="0" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="739">
@@ -16749,7 +16749,7 @@
         </is>
       </c>
       <c r="F739" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="740">
@@ -16770,7 +16770,7 @@
         </is>
       </c>
       <c r="F740" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="741">
@@ -16791,7 +16791,7 @@
         </is>
       </c>
       <c r="F741" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="742">
@@ -16812,7 +16812,7 @@
         </is>
       </c>
       <c r="F742" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="743">
@@ -16833,7 +16833,7 @@
         </is>
       </c>
       <c r="F743" s="0" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="744">
@@ -16854,7 +16854,7 @@
         </is>
       </c>
       <c r="F744" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="745">
@@ -16875,7 +16875,7 @@
         </is>
       </c>
       <c r="F745" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="746">
@@ -16896,7 +16896,7 @@
         </is>
       </c>
       <c r="F746" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="747">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="F747" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="748">
@@ -16938,7 +16938,7 @@
         </is>
       </c>
       <c r="F748" s="0" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="749">
@@ -16959,7 +16959,7 @@
         </is>
       </c>
       <c r="F749" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="750">
@@ -16980,7 +16980,7 @@
         </is>
       </c>
       <c r="F750" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="751">
@@ -17001,7 +17001,7 @@
         </is>
       </c>
       <c r="F751" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="752">
@@ -17022,7 +17022,7 @@
         </is>
       </c>
       <c r="F752" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="753">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="F753" s="0" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/RoundData.xlsx
+++ b/Luban/Config/Datas/RoundData.xlsx
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="F4" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="F5" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F6" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" customFormat="1" s="2">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="F12" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L12" s="13" t="n"/>
       <c r="M12" s="13" t="n"/>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="F13" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L13" s="13" t="n"/>
       <c r="M13" s="13" t="n"/>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="F14" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="F15" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L15" s="13" t="n"/>
       <c r="M15" s="13" t="n"/>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="F16" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" s="1">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="F17" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="1">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F18" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="1">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F19" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="1">
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="F20" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" s="1">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="F21" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F22" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="F23" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="F24" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="F25" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="F26" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="F27" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="F28" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="F29" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="F30" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="F31" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="F32" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="F33" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F34" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="F35" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="F36" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="F37" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F38" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F39" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="F40" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="F41" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="F42" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="F43" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="F44" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="F45" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="F46" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="F47" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="F48" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="F49" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="F50" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="F51" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F52" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="F53" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54">
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="F54" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="F55" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F56" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="F57" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="F58" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59">
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="F59" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="F60" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="F61" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62">
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="F62" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="F63" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="F64" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="F65" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="F66" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="F67" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68">
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="F68" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="F69" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="F70" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="F71" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72">
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="F72" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="F73" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="F74" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="F75" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="F76" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="F77" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78">
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="F78" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F79" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="F80" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="F81" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="F82" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83">
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="F83" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84">
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="F84" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="F85" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="F86" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="F87" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="F88" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89">
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="F89" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90">
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="F90" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="F91" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="F92" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F93" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="F94" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F95" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="F96" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F97" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="98">
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="F98" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="99">
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="F99" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100">
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="F100" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="F101" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102">
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="F102" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103">
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="F103" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104">
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="F104" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F105" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="F106" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107">
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="F107" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108">
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="F108" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="F109" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="F110" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="F111" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112">
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="F112" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="F113" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114">
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="F114" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115">
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="F115" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="F116" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="117">
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="F117" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="118">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="F118" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="119">
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F119" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120">
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="F120" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121">
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="F121" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="F122" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="F123" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124">
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="F124" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="F125" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="F126" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127">
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="F127" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128">
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="F128" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="F129" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130">
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="F130" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="F131" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="132">
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="F132" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="133">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="F133" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="134">
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="F134" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135">
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="F135" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="136">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="F136" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="F137" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="138">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F138" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139">
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="F139" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="140">
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="F140" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="141">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="F141" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142">
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="F142" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="F143" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144">
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="F144" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="F145" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="F146" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147">
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="F147" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="148">
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="F148" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="F149" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="150">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="F150" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="151">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="F151" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="152">
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="F152" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F153" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="154">
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="F154" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="F155" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="156">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="F156" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="157">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="F157" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="158">
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="F158" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="159">
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="F159" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="160">
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="F160" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="161">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="F161" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="162">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="F162" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="163">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="F163" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="F164" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="F165" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="166">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="F166" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="F167" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="168">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="F168" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="169">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="F169" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="F170" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="171">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="F171" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="172">
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="F172" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="173">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="F173" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="174">
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="F174" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="175">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="F175" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="176">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="F176" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="177">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="F177" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="178">
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="F178" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="179">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="F179" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="180">
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="F180" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="181">
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="F181" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="182">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="F182" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="183">
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="F183" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="184">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="F184" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="185">
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="F185" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="186">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="F186" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="187">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="F187" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="188">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="F188" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="189">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="F189" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="190">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="F190" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="191">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="F191" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="192">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="F192" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="193">
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="F193" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="194">
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="F194" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="195">
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="F195" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="196">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="F196" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="197">
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="F197" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="198">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="F198" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="199">
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="F199" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="200">
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="F200" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="201">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="F201" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="202">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="F202" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="203">
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="F203" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="204">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="F204" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="205">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="F205" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="206">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="F206" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="207">
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="F207" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="208">
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="F208" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="209">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="F209" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="210">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="F210" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="211">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="F211" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="212">
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="F212" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="213">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="F213" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="214">
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="F214" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="215">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="F215" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="216">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="F216" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="217">
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="F217" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="218">
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="F218" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="219">
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="F219" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="220">
@@ -5850,7 +5850,7 @@
         </is>
       </c>
       <c r="F220" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="221">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="F221" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="222">
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="F222" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="223">
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="F223" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="224">
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="F224" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225">
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="F225" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="226">
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="F226" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="227">
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="F227" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="228">
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="F228" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="229">
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="F229" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="230">
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="F230" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="231">
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="F231" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="232">
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="F232" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="233">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="F233" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="234">
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="F234" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="235">
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="F235" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="236">
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="F236" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="237">
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="F237" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="238">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="F238" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="239">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="F239" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="240">
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="F240" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="241">
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="F241" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="242">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="F242" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="243">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="F243" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="244">
@@ -6354,7 +6354,7 @@
         </is>
       </c>
       <c r="F244" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="245">
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="F245" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="246">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="F246" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="247">
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="F247" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="248">
@@ -6438,7 +6438,7 @@
         </is>
       </c>
       <c r="F248" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="249">
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="F249" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="250">
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="F250" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="251">
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="F251" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="252">
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="F252" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="253">
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="F253" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="254">
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="F254" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="255">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="F255" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="256">
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="F256" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="257">
@@ -6627,7 +6627,7 @@
         </is>
       </c>
       <c r="F257" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="258">
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="F258" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="259">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="F259" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="260">
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="F260" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="261">
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="F261" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="262">
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="F262" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="263">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="F263" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="264">
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="F264" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="265">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="F265" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="266">
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="F266" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="267">
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="F267" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="268">
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="F268" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="269">
@@ -6879,7 +6879,7 @@
         </is>
       </c>
       <c r="F269" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="270">
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="F270" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="271">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="F271" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="272">
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="F272" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="273">
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="F273" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="274">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="F274" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="275">
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="F275" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="276">
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="F276" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="277">
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="F277" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="278">
@@ -7068,7 +7068,7 @@
         </is>
       </c>
       <c r="F278" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="279">
@@ -7089,7 +7089,7 @@
         </is>
       </c>
       <c r="F279" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="280">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="F280" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="281">
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="F281" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="282">
@@ -7152,7 +7152,7 @@
         </is>
       </c>
       <c r="F282" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="283">
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="F283" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="284">
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="F284" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="285">
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="F285" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="286">
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="F286" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="287">
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="F287" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="288">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="F288" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="289">
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="F289" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="290">
@@ -7320,7 +7320,7 @@
         </is>
       </c>
       <c r="F290" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="291">
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="F291" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="292">
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="F292" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="293">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="F293" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="294">
@@ -7404,7 +7404,7 @@
         </is>
       </c>
       <c r="F294" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="295">
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="F295" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="296">
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="F296" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="297">
@@ -7467,7 +7467,7 @@
         </is>
       </c>
       <c r="F297" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="298">
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="F298" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="299">
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="F299" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="300">
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="F300" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="301">
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="F301" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="302">
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="F302" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="303">
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="F303" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="304">
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="F304" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="305">
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="F305" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="306">
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="F306" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="307">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="F307" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="308">
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="F308" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="309">
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="F309" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="310">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="F310" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="311">
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="F311" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="312">
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="F312" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="313">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="F313" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="314">
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="F314" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="315">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="F315" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="316">
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="F316" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="317">
@@ -7887,7 +7887,7 @@
         </is>
       </c>
       <c r="F317" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="318">
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="F318" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="319">
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="F319" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="320">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="F320" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="321">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="F321" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="322">
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="F322" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="323">
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="F323" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="324">
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="F324" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="325">
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="F325" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="326">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="F326" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="327">
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="F327" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="328">
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="F328" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="329">
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="F329" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="330">
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="F330" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="331">
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="F331" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="332">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="F332" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="333">
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F333" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="334">
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="F334" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="335">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="F335" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="336">
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="F336" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="337">
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="F337" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="338">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="F338" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="339">
@@ -8349,7 +8349,7 @@
         </is>
       </c>
       <c r="F339" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="340">
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="F340" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="341">
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="F341" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="342">
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="F342" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="343">
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="F343" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="344">
@@ -8454,7 +8454,7 @@
         </is>
       </c>
       <c r="F344" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="345">
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="F345" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="346">
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="F346" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="347">
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F347" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="348">
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="F348" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="349">
@@ -8559,7 +8559,7 @@
         </is>
       </c>
       <c r="F349" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="350">
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="F350" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="351">
@@ -8601,7 +8601,7 @@
         </is>
       </c>
       <c r="F351" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="352">
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="F352" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="353">
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="F353" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="354">
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="F354" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="355">
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="F355" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="356">
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="F356" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="357">
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="F357" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="358">
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="F358" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="359">
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="F359" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="360">
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="F360" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="361">
@@ -8811,7 +8811,7 @@
         </is>
       </c>
       <c r="F361" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="362">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="F362" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="363">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="F363" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="364">
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="F364" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="365">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="F365" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="366">
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="F366" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="367">
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="F367" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="368">
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="F368" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="369">
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="F369" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="370">
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="F370" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="371">
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="F371" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="372">
@@ -9042,7 +9042,7 @@
         </is>
       </c>
       <c r="F372" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="373">
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="F373" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="374">
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="F374" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="375">
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="F375" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="376">
@@ -9126,7 +9126,7 @@
         </is>
       </c>
       <c r="F376" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="377">
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="F377" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="378">
@@ -9168,7 +9168,7 @@
         </is>
       </c>
       <c r="F378" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="379">
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="F379" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="380">
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="F380" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="381">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="F381" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="382">
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="F382" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="383">
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="F383" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="384">
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="F384" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="385">
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="F385" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="386">
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="F386" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="387">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="F387" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="388">
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="F388" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="389">
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="F389" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="390">
@@ -9420,7 +9420,7 @@
         </is>
       </c>
       <c r="F390" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="391">
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="F391" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="392">
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="F392" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="393">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="F393" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="394">
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="F394" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="395">
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="F395" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="396">
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="F396" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="397">
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="F397" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="398">
@@ -9588,7 +9588,7 @@
         </is>
       </c>
       <c r="F398" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="399">
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="F399" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="400">
@@ -9630,7 +9630,7 @@
         </is>
       </c>
       <c r="F400" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="401">
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="F401" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="402">
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="F402" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="403">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="F403" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="404">
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="F404" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="405">
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="F405" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="406">
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="F406" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="407">
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="F407" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="408">
@@ -9798,7 +9798,7 @@
         </is>
       </c>
       <c r="F408" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="409">
@@ -9819,7 +9819,7 @@
         </is>
       </c>
       <c r="F409" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="410">
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="F410" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="411">
@@ -9861,7 +9861,7 @@
         </is>
       </c>
       <c r="F411" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="412">
@@ -9882,7 +9882,7 @@
         </is>
       </c>
       <c r="F412" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="413">
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="F413" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="414">
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="F414" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="415">
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="F415" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="416">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="F416" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="417">
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="F417" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="418">
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="F418" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="419">
@@ -10029,7 +10029,7 @@
         </is>
       </c>
       <c r="F419" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="420">
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="F420" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="421">
@@ -10071,7 +10071,7 @@
         </is>
       </c>
       <c r="F421" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="422">
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="F422" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="423">
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="F423" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="424">
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="F424" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="425">
@@ -10155,7 +10155,7 @@
         </is>
       </c>
       <c r="F425" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="426">
@@ -10176,7 +10176,7 @@
         </is>
       </c>
       <c r="F426" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="427">
@@ -10197,7 +10197,7 @@
         </is>
       </c>
       <c r="F427" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="428">
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="F428" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="429">
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="F429" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="430">
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="F430" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="431">
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="F431" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="432">
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="F432" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="433">
@@ -10323,7 +10323,7 @@
         </is>
       </c>
       <c r="F433" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="434">
@@ -10344,7 +10344,7 @@
         </is>
       </c>
       <c r="F434" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="435">
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="F435" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="436">
@@ -10386,7 +10386,7 @@
         </is>
       </c>
       <c r="F436" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="437">
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="F437" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="438">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="F438" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="439">
@@ -10449,7 +10449,7 @@
         </is>
       </c>
       <c r="F439" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="440">
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="F440" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="441">
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="F441" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="442">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="F442" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="443">
@@ -10533,7 +10533,7 @@
         </is>
       </c>
       <c r="F443" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="444">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="F444" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="445">
@@ -10575,7 +10575,7 @@
         </is>
       </c>
       <c r="F445" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="446">
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="F446" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="447">
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="F447" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="448">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="F448" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="449">
@@ -10659,7 +10659,7 @@
         </is>
       </c>
       <c r="F449" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="450">
@@ -10680,7 +10680,7 @@
         </is>
       </c>
       <c r="F450" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="451">
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="F451" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="452">
@@ -10722,7 +10722,7 @@
         </is>
       </c>
       <c r="F452" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="453">
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="F453" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="454">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="F454" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="455">
@@ -10785,7 +10785,7 @@
         </is>
       </c>
       <c r="F455" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="456">
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="F456" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="457">
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="F457" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="458">
@@ -10848,7 +10848,7 @@
         </is>
       </c>
       <c r="F458" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="459">
@@ -10869,7 +10869,7 @@
         </is>
       </c>
       <c r="F459" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="460">
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="F460" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="461">
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="F461" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="462">
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="F462" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="463">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="F463" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="464">
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="F464" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="465">
@@ -10995,7 +10995,7 @@
         </is>
       </c>
       <c r="F465" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="466">
@@ -11016,7 +11016,7 @@
         </is>
       </c>
       <c r="F466" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="467">
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="F467" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="468">
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="F468" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="469">
@@ -11079,7 +11079,7 @@
         </is>
       </c>
       <c r="F469" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="470">
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="F470" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="471">
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="F471" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="472">
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="F472" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="473">
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="F473" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="474">
@@ -11184,7 +11184,7 @@
         </is>
       </c>
       <c r="F474" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="475">
@@ -11205,7 +11205,7 @@
         </is>
       </c>
       <c r="F475" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="476">
@@ -11226,7 +11226,7 @@
         </is>
       </c>
       <c r="F476" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="477">
@@ -11247,7 +11247,7 @@
         </is>
       </c>
       <c r="F477" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="478">
@@ -11268,7 +11268,7 @@
         </is>
       </c>
       <c r="F478" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="479">
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="F479" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="480">
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="F480" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="481">
@@ -11331,7 +11331,7 @@
         </is>
       </c>
       <c r="F481" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="482">
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="F482" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="483">
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="F483" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="484">
@@ -11394,7 +11394,7 @@
         </is>
       </c>
       <c r="F484" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="485">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="F485" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="486">
@@ -11436,7 +11436,7 @@
         </is>
       </c>
       <c r="F486" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="487">
@@ -11457,7 +11457,7 @@
         </is>
       </c>
       <c r="F487" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="488">
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="F488" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="489">
@@ -11499,7 +11499,7 @@
         </is>
       </c>
       <c r="F489" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="490">
@@ -11520,7 +11520,7 @@
         </is>
       </c>
       <c r="F490" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="491">
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="F491" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="492">
@@ -11562,7 +11562,7 @@
         </is>
       </c>
       <c r="F492" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="493">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="F493" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="494">
@@ -11604,7 +11604,7 @@
         </is>
       </c>
       <c r="F494" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="495">
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="F495" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="496">
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="F496" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="497">
@@ -11667,7 +11667,7 @@
         </is>
       </c>
       <c r="F497" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="498">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="F498" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="499">
@@ -11709,7 +11709,7 @@
         </is>
       </c>
       <c r="F499" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="500">
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="F500" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="501">
@@ -11751,7 +11751,7 @@
         </is>
       </c>
       <c r="F501" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="502">
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="F502" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="503">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="F503" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="504">
@@ -11814,7 +11814,7 @@
         </is>
       </c>
       <c r="F504" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="505">
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="F505" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="506">
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="F506" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="507">
@@ -11877,7 +11877,7 @@
         </is>
       </c>
       <c r="F507" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="508">
@@ -11898,7 +11898,7 @@
         </is>
       </c>
       <c r="F508" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="509">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="F509" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="510">
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="F510" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="511">
@@ -11961,7 +11961,7 @@
         </is>
       </c>
       <c r="F511" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="512">
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="F512" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="513">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="F513" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="514">
@@ -12024,7 +12024,7 @@
         </is>
       </c>
       <c r="F514" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="515">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="F515" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="516">
@@ -12066,7 +12066,7 @@
         </is>
       </c>
       <c r="F516" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="517">
@@ -12087,7 +12087,7 @@
         </is>
       </c>
       <c r="F517" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="518">
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="F518" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="519">
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="F519" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="520">
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="F520" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="521">
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="F521" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="522">
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="F522" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="523">
@@ -12213,7 +12213,7 @@
         </is>
       </c>
       <c r="F523" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="524">
@@ -12234,7 +12234,7 @@
         </is>
       </c>
       <c r="F524" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="525">
@@ -12255,7 +12255,7 @@
         </is>
       </c>
       <c r="F525" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="526">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="F526" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="527">
@@ -12297,7 +12297,7 @@
         </is>
       </c>
       <c r="F527" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="528">
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="F528" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="529">
@@ -12339,7 +12339,7 @@
         </is>
       </c>
       <c r="F529" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="530">
@@ -12360,7 +12360,7 @@
         </is>
       </c>
       <c r="F530" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="531">
@@ -12381,7 +12381,7 @@
         </is>
       </c>
       <c r="F531" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="532">
@@ -12402,7 +12402,7 @@
         </is>
       </c>
       <c r="F532" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="533">
@@ -12423,7 +12423,7 @@
         </is>
       </c>
       <c r="F533" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="534">
@@ -12444,7 +12444,7 @@
         </is>
       </c>
       <c r="F534" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="535">
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="F535" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="536">
@@ -12486,7 +12486,7 @@
         </is>
       </c>
       <c r="F536" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="537">
@@ -12507,7 +12507,7 @@
         </is>
       </c>
       <c r="F537" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="538">
@@ -12528,7 +12528,7 @@
         </is>
       </c>
       <c r="F538" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="539">
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="F539" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="540">
@@ -12570,7 +12570,7 @@
         </is>
       </c>
       <c r="F540" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="541">
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="F541" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="542">
@@ -12612,7 +12612,7 @@
         </is>
       </c>
       <c r="F542" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="543">
@@ -12633,7 +12633,7 @@
         </is>
       </c>
       <c r="F543" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="544">
@@ -12654,7 +12654,7 @@
         </is>
       </c>
       <c r="F544" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="545">
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="F545" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="546">
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="F546" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="547">
@@ -12717,7 +12717,7 @@
         </is>
       </c>
       <c r="F547" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="548">
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="F548" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="549">
@@ -12759,7 +12759,7 @@
         </is>
       </c>
       <c r="F549" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="550">
@@ -12780,7 +12780,7 @@
         </is>
       </c>
       <c r="F550" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="551">
@@ -12801,7 +12801,7 @@
         </is>
       </c>
       <c r="F551" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="552">
@@ -12822,7 +12822,7 @@
         </is>
       </c>
       <c r="F552" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="553">
@@ -12843,7 +12843,7 @@
         </is>
       </c>
       <c r="F553" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="554">
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="F554" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="555">
@@ -12885,7 +12885,7 @@
         </is>
       </c>
       <c r="F555" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="556">
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="F556" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="557">
@@ -12927,7 +12927,7 @@
         </is>
       </c>
       <c r="F557" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="558">
@@ -12948,7 +12948,7 @@
         </is>
       </c>
       <c r="F558" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="559">
@@ -12969,7 +12969,7 @@
         </is>
       </c>
       <c r="F559" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="560">
@@ -12990,7 +12990,7 @@
         </is>
       </c>
       <c r="F560" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="561">
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="F561" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="562">
@@ -13032,7 +13032,7 @@
         </is>
       </c>
       <c r="F562" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="563">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="F563" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="564">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="F564" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="565">
@@ -13095,7 +13095,7 @@
         </is>
       </c>
       <c r="F565" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="566">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="F566" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="567">
@@ -13137,7 +13137,7 @@
         </is>
       </c>
       <c r="F567" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="568">
@@ -13158,7 +13158,7 @@
         </is>
       </c>
       <c r="F568" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="569">
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="F569" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="570">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="F570" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="571">
@@ -13221,7 +13221,7 @@
         </is>
       </c>
       <c r="F571" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="572">
@@ -13242,7 +13242,7 @@
         </is>
       </c>
       <c r="F572" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="573">
@@ -13263,7 +13263,7 @@
         </is>
       </c>
       <c r="F573" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="574">
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="F574" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="575">
@@ -13305,7 +13305,7 @@
         </is>
       </c>
       <c r="F575" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="576">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="F576" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="577">
@@ -13347,7 +13347,7 @@
         </is>
       </c>
       <c r="F577" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="578">
@@ -13368,7 +13368,7 @@
         </is>
       </c>
       <c r="F578" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="579">
@@ -13389,7 +13389,7 @@
         </is>
       </c>
       <c r="F579" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="580">
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="F580" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="581">
@@ -13431,7 +13431,7 @@
         </is>
       </c>
       <c r="F581" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="582">
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="F582" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="583">
@@ -13473,7 +13473,7 @@
         </is>
       </c>
       <c r="F583" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="584">
@@ -13494,7 +13494,7 @@
         </is>
       </c>
       <c r="F584" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="585">
@@ -13515,7 +13515,7 @@
         </is>
       </c>
       <c r="F585" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="586">
@@ -13536,7 +13536,7 @@
         </is>
       </c>
       <c r="F586" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="587">
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F587" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="588">
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="F588" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="589">
@@ -13599,7 +13599,7 @@
         </is>
       </c>
       <c r="F589" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="590">
@@ -13620,7 +13620,7 @@
         </is>
       </c>
       <c r="F590" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="591">
@@ -13641,7 +13641,7 @@
         </is>
       </c>
       <c r="F591" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="592">
@@ -13662,7 +13662,7 @@
         </is>
       </c>
       <c r="F592" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="593">
@@ -13683,7 +13683,7 @@
         </is>
       </c>
       <c r="F593" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="594">
@@ -13704,7 +13704,7 @@
         </is>
       </c>
       <c r="F594" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="595">
@@ -13725,7 +13725,7 @@
         </is>
       </c>
       <c r="F595" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="596">
@@ -13746,7 +13746,7 @@
         </is>
       </c>
       <c r="F596" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="597">
@@ -13767,7 +13767,7 @@
         </is>
       </c>
       <c r="F597" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="598">
@@ -13788,7 +13788,7 @@
         </is>
       </c>
       <c r="F598" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="599">
@@ -13809,7 +13809,7 @@
         </is>
       </c>
       <c r="F599" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="600">
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="F600" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="601">
@@ -13851,7 +13851,7 @@
         </is>
       </c>
       <c r="F601" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="602">
@@ -13872,7 +13872,7 @@
         </is>
       </c>
       <c r="F602" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="603">
@@ -13893,7 +13893,7 @@
         </is>
       </c>
       <c r="F603" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="604">
@@ -13914,7 +13914,7 @@
         </is>
       </c>
       <c r="F604" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="605">
@@ -13935,7 +13935,7 @@
         </is>
       </c>
       <c r="F605" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="606">
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="F606" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="607">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="F607" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="608">
@@ -13998,7 +13998,7 @@
         </is>
       </c>
       <c r="F608" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="609">
@@ -14019,7 +14019,7 @@
         </is>
       </c>
       <c r="F609" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="610">
@@ -14040,7 +14040,7 @@
         </is>
       </c>
       <c r="F610" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="611">
@@ -14061,7 +14061,7 @@
         </is>
       </c>
       <c r="F611" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="612">
@@ -14082,7 +14082,7 @@
         </is>
       </c>
       <c r="F612" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="613">
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="F613" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="614">
@@ -14124,7 +14124,7 @@
         </is>
       </c>
       <c r="F614" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="615">
@@ -14145,7 +14145,7 @@
         </is>
       </c>
       <c r="F615" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="616">
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="F616" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="617">
@@ -14187,7 +14187,7 @@
         </is>
       </c>
       <c r="F617" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="618">
@@ -14208,7 +14208,7 @@
         </is>
       </c>
       <c r="F618" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="619">
@@ -14229,7 +14229,7 @@
         </is>
       </c>
       <c r="F619" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="620">
@@ -14250,7 +14250,7 @@
         </is>
       </c>
       <c r="F620" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="621">
@@ -14271,7 +14271,7 @@
         </is>
       </c>
       <c r="F621" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="622">
@@ -14292,7 +14292,7 @@
         </is>
       </c>
       <c r="F622" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="623">
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="F623" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="624">
@@ -14334,7 +14334,7 @@
         </is>
       </c>
       <c r="F624" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="625">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="F625" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="626">
@@ -14376,7 +14376,7 @@
         </is>
       </c>
       <c r="F626" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="627">
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="F627" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="628">
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="F628" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="629">
@@ -14439,7 +14439,7 @@
         </is>
       </c>
       <c r="F629" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="630">
@@ -14460,7 +14460,7 @@
         </is>
       </c>
       <c r="F630" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="631">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="F631" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="632">
@@ -14502,7 +14502,7 @@
         </is>
       </c>
       <c r="F632" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="633">
@@ -14523,7 +14523,7 @@
         </is>
       </c>
       <c r="F633" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="634">
@@ -14544,7 +14544,7 @@
         </is>
       </c>
       <c r="F634" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="635">
@@ -14565,7 +14565,7 @@
         </is>
       </c>
       <c r="F635" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="636">
@@ -14586,7 +14586,7 @@
         </is>
       </c>
       <c r="F636" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="637">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="F637" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="638">
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="F638" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="639">
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="F639" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="640">
@@ -14670,7 +14670,7 @@
         </is>
       </c>
       <c r="F640" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="641">
@@ -14691,7 +14691,7 @@
         </is>
       </c>
       <c r="F641" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="642">
@@ -14712,7 +14712,7 @@
         </is>
       </c>
       <c r="F642" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="643">
@@ -14733,7 +14733,7 @@
         </is>
       </c>
       <c r="F643" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="644">
@@ -14754,7 +14754,7 @@
         </is>
       </c>
       <c r="F644" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="645">
@@ -14775,7 +14775,7 @@
         </is>
       </c>
       <c r="F645" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="646">
@@ -14796,7 +14796,7 @@
         </is>
       </c>
       <c r="F646" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="647">
@@ -14817,7 +14817,7 @@
         </is>
       </c>
       <c r="F647" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="648">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="F648" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="649">
@@ -14859,7 +14859,7 @@
         </is>
       </c>
       <c r="F649" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="650">
@@ -14880,7 +14880,7 @@
         </is>
       </c>
       <c r="F650" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="651">
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="F651" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="652">
@@ -14922,7 +14922,7 @@
         </is>
       </c>
       <c r="F652" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="653">
@@ -14943,7 +14943,7 @@
         </is>
       </c>
       <c r="F653" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="654">
@@ -14964,7 +14964,7 @@
         </is>
       </c>
       <c r="F654" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="655">
@@ -14985,7 +14985,7 @@
         </is>
       </c>
       <c r="F655" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="656">
@@ -15006,7 +15006,7 @@
         </is>
       </c>
       <c r="F656" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="657">
@@ -15027,7 +15027,7 @@
         </is>
       </c>
       <c r="F657" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="658">
@@ -15048,7 +15048,7 @@
         </is>
       </c>
       <c r="F658" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="659">
@@ -15069,7 +15069,7 @@
         </is>
       </c>
       <c r="F659" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="660">
@@ -15090,7 +15090,7 @@
         </is>
       </c>
       <c r="F660" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="661">
@@ -15111,7 +15111,7 @@
         </is>
       </c>
       <c r="F661" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="662">
@@ -15132,7 +15132,7 @@
         </is>
       </c>
       <c r="F662" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="663">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="F663" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="664">
@@ -15174,7 +15174,7 @@
         </is>
       </c>
       <c r="F664" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="665">
@@ -15195,7 +15195,7 @@
         </is>
       </c>
       <c r="F665" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="666">
@@ -15216,7 +15216,7 @@
         </is>
       </c>
       <c r="F666" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="667">
@@ -15237,7 +15237,7 @@
         </is>
       </c>
       <c r="F667" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="668">
@@ -15258,7 +15258,7 @@
         </is>
       </c>
       <c r="F668" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="669">
@@ -15279,7 +15279,7 @@
         </is>
       </c>
       <c r="F669" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="670">
@@ -15300,7 +15300,7 @@
         </is>
       </c>
       <c r="F670" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="671">
@@ -15321,7 +15321,7 @@
         </is>
       </c>
       <c r="F671" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="672">
@@ -15342,7 +15342,7 @@
         </is>
       </c>
       <c r="F672" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="673">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="F673" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="674">
@@ -15384,7 +15384,7 @@
         </is>
       </c>
       <c r="F674" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="675">
@@ -15405,7 +15405,7 @@
         </is>
       </c>
       <c r="F675" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="676">
@@ -15426,7 +15426,7 @@
         </is>
       </c>
       <c r="F676" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="677">
@@ -15447,7 +15447,7 @@
         </is>
       </c>
       <c r="F677" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="678">
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="F678" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="679">
@@ -15489,7 +15489,7 @@
         </is>
       </c>
       <c r="F679" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="680">
@@ -15510,7 +15510,7 @@
         </is>
       </c>
       <c r="F680" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="681">
@@ -15531,7 +15531,7 @@
         </is>
       </c>
       <c r="F681" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="682">
@@ -15552,7 +15552,7 @@
         </is>
       </c>
       <c r="F682" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="683">
@@ -15573,7 +15573,7 @@
         </is>
       </c>
       <c r="F683" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="684">
@@ -15594,7 +15594,7 @@
         </is>
       </c>
       <c r="F684" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="685">
@@ -15615,7 +15615,7 @@
         </is>
       </c>
       <c r="F685" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="686">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="F686" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="687">
@@ -15657,7 +15657,7 @@
         </is>
       </c>
       <c r="F687" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="688">
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="F688" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="689">
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="F689" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="690">
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="F690" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="691">
@@ -15741,7 +15741,7 @@
         </is>
       </c>
       <c r="F691" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="692">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="F692" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="693">
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="F693" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="694">
@@ -15804,7 +15804,7 @@
         </is>
       </c>
       <c r="F694" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="695">
@@ -15825,7 +15825,7 @@
         </is>
       </c>
       <c r="F695" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="696">
@@ -15846,7 +15846,7 @@
         </is>
       </c>
       <c r="F696" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="697">
@@ -15867,7 +15867,7 @@
         </is>
       </c>
       <c r="F697" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="698">
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="F698" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="699">
@@ -15909,7 +15909,7 @@
         </is>
       </c>
       <c r="F699" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="700">
@@ -15930,7 +15930,7 @@
         </is>
       </c>
       <c r="F700" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="701">
@@ -15951,7 +15951,7 @@
         </is>
       </c>
       <c r="F701" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="702">
@@ -15972,7 +15972,7 @@
         </is>
       </c>
       <c r="F702" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="703">
@@ -15993,7 +15993,7 @@
         </is>
       </c>
       <c r="F703" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="704">
@@ -16014,7 +16014,7 @@
         </is>
       </c>
       <c r="F704" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="705">
@@ -16035,7 +16035,7 @@
         </is>
       </c>
       <c r="F705" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="706">
@@ -16056,7 +16056,7 @@
         </is>
       </c>
       <c r="F706" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="707">
@@ -16077,7 +16077,7 @@
         </is>
       </c>
       <c r="F707" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="708">
@@ -16098,7 +16098,7 @@
         </is>
       </c>
       <c r="F708" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="709">
@@ -16119,7 +16119,7 @@
         </is>
       </c>
       <c r="F709" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="710">
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="F710" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="711">
@@ -16161,7 +16161,7 @@
         </is>
       </c>
       <c r="F711" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="712">
@@ -16182,7 +16182,7 @@
         </is>
       </c>
       <c r="F712" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="713">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="F713" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="714">
@@ -16224,7 +16224,7 @@
         </is>
       </c>
       <c r="F714" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="715">
@@ -16245,7 +16245,7 @@
         </is>
       </c>
       <c r="F715" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="716">
@@ -16266,7 +16266,7 @@
         </is>
       </c>
       <c r="F716" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="717">
@@ -16287,7 +16287,7 @@
         </is>
       </c>
       <c r="F717" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="718">
@@ -16308,7 +16308,7 @@
         </is>
       </c>
       <c r="F718" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="719">
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="F719" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="720">
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="F720" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="721">
@@ -16371,7 +16371,7 @@
         </is>
       </c>
       <c r="F721" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="722">
@@ -16392,7 +16392,7 @@
         </is>
       </c>
       <c r="F722" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="723">
@@ -16413,7 +16413,7 @@
         </is>
       </c>
       <c r="F723" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="724">
@@ -16434,7 +16434,7 @@
         </is>
       </c>
       <c r="F724" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="725">
@@ -16455,7 +16455,7 @@
         </is>
       </c>
       <c r="F725" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="726">
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="F726" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="727">
@@ -16497,7 +16497,7 @@
         </is>
       </c>
       <c r="F727" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="728">
@@ -16518,7 +16518,7 @@
         </is>
       </c>
       <c r="F728" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="729">
@@ -16539,7 +16539,7 @@
         </is>
       </c>
       <c r="F729" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="730">
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="F730" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="731">
@@ -16581,7 +16581,7 @@
         </is>
       </c>
       <c r="F731" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="732">
@@ -16602,7 +16602,7 @@
         </is>
       </c>
       <c r="F732" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="733">
@@ -16623,7 +16623,7 @@
         </is>
       </c>
       <c r="F733" s="0" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="734">
@@ -16644,7 +16644,7 @@
         </is>
       </c>
       <c r="F734" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="735">
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="F735" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="736">
@@ -16686,7 +16686,7 @@
         </is>
       </c>
       <c r="F736" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="737">
@@ -16707,7 +16707,7 @@
         </is>
       </c>
       <c r="F737" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="738">
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="F738" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="739">
@@ -16749,7 +16749,7 @@
         </is>
       </c>
       <c r="F739" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="740">
@@ -16770,7 +16770,7 @@
         </is>
       </c>
       <c r="F740" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="741">
@@ -16791,7 +16791,7 @@
         </is>
       </c>
       <c r="F741" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="742">
@@ -16812,7 +16812,7 @@
         </is>
       </c>
       <c r="F742" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="743">
@@ -16833,7 +16833,7 @@
         </is>
       </c>
       <c r="F743" s="0" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="744">
@@ -16854,7 +16854,7 @@
         </is>
       </c>
       <c r="F744" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="745">
@@ -16875,7 +16875,7 @@
         </is>
       </c>
       <c r="F745" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="746">
@@ -16896,7 +16896,7 @@
         </is>
       </c>
       <c r="F746" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="747">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="F747" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="748">
@@ -16938,7 +16938,7 @@
         </is>
       </c>
       <c r="F748" s="0" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="749">
@@ -16959,7 +16959,7 @@
         </is>
       </c>
       <c r="F749" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="750">
@@ -16980,7 +16980,7 @@
         </is>
       </c>
       <c r="F750" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="751">
@@ -17001,7 +17001,7 @@
         </is>
       </c>
       <c r="F751" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="752">
@@ -17022,7 +17022,7 @@
         </is>
       </c>
       <c r="F752" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="753">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="F753" s="0" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
